--- a/docs/exports/week-2026-10-25.xlsx
+++ b/docs/exports/week-2026-10-25.xlsx
@@ -151,7 +151,7 @@
         <v>46319</v>
       </c>
     </row>
-    <row r="4" ht="82" customHeight="1">
+    <row r="4" ht="98" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02</t>
@@ -166,58 +166,60 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">颱風後電網復原與智慧工廠設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台電 10 月 24 日下午通報全台逾 34 萬戶曾停電、已復電逾 9 成；雲林局部線路因鹽塵害增加搶修工序。中華電信另成立智慧影像子公司，現階段沒有工廠停線損失或新裝機量數據。</t>
+            <t xml:space="preserve">颱風後供電復原與工廠電力、智慧系統
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">10 月 24 日台電通報全台累計逾 34 萬戶曾停電，宜蘭區處於 25 日宣布下午 4 時完成逾 3 萬受災民生用戶復電；各項數字分屬不同時點和地區，尚無半導體工廠停機資料。中華電信另公布智慧影像子公司成立，未揭露工業端裝機量。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">10/22、10/24、10/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="98" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">東南亞海纜招標與馬來西亞資料中心投資意向
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">MViSTA 海纜開發商提出約 4 億美元建置估算與 2028 年底啟用目標；馬來西亞總理 24 日另轉述 500 億美元 AI／資料中心投資意向，媒體 25 日指涉 SoftBank 孫正義。兩案均缺少實際施工、併網及完工驗證，且投資金額不可視為已支出。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">10/22、10/24</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="82" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">東南亞四國海纜招標及越南機房規劃
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 開發商表示串聯馬來西亞、越南、新加坡及泰國的 2,500 公里海纜仍在招標，成本預估約 4 億美元、目標 2028 年底啟用。美國 USTDA 資助的胡志明市機房可行性研究與海纜工程是不同階段。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C5" s="6">
-        <v>46317</v>
-      </c>
-    </row>
-    <row r="6" ht="82" customHeight="1">
+    <row r="6" ht="98" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">04</t>
@@ -232,21 +234,23 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">玉晶光與 3M 光互連合作及自結財務
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光 10 月 23 日公告 9 月自結歸母淨利約 4.34 億元、年減 15%，媒體另報導約 48.13 億元的 3M 私募股款已入帳。EBO、CPO 產品仍在合作開發及認證階段。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C6" s="6">
-        <v>46318</v>
+            <t xml:space="preserve">台灣光互連合作與高科技設備物流
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光與 3M 的光互連合作尚未確認量產交付；長榮航總經理 10 月 25 日稱 AI 伺服器等高科技貨運需求持續，但也指出航空燃油成本壓力。長榮航 9 月貨運營收年增 42.55%，為已公布的歷史營收數據，沒有拆分 AI 貨物量價。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/23、10/25</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="82" customHeight="1">
@@ -438,7 +442,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="310" customHeight="1">
+    <row r="6" ht="242" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">04</t>
@@ -453,6 +457,43 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">追蹤：台電宜蘭 10 月 25 日 16 時完成逾 3 萬戶復電
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台電宜蘭區營業處 10 月 25 日公告，薔琵颱風造成宜蘭累計逾 3 萬戶受災民生用戶停電，經跨區搶修，當日下午 4 時已完成復電。台電新竹區處另確認當地累計 10,886 戶曾停電，已於 10 月 24 日晚間 9 時全數復電；兩項均為區域配電數據，未公開晶圓廠設備停機或良率損失。受災線路包含山區與沿海配電設備，主要因素為強風、樹竹碰觸及高低壓線路斷落。新竹工業區與半導體供應鏈用電可靠性需透過廠區自身電力紀錄判定，不能用民生復電數據直接推估工廠產線損失。10 月 25 日新增事實為宜蘭區處宣布在 16 時完成受災民生用戶全數復電；10 月 24 日全台累計逾 34 萬戶曾停電為前一期已公布資料。新竹的全數復電為 10 月 24 日晚間發布的另項地區實績。台電仍提醒個別偏遠末端線路住戶可能需另外報修，因此公告中的「全數復電」係指已掌握的受災民生用戶。數字未提供實際用電負載或高科技工廠停線時數。個別半導體設備機台、資料中心、工廠產線的停機紀錄與生產影響未公布，且台電仍受理零星用戶報修。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製程電源、UPS 和廠務監控供應商可查明各廠是否有實際電壓驟降、儲能切換或異常警報。家庭戶數復電不揭露機台開機狀態，因此不能換算設備停產或備援採購。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="310" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">MViSTA 海纜開發商稱將於 10 月決標，規劃串聯東南亞四國與越南資料中心
 </t>
           </r>
@@ -466,53 +507,16 @@
           </r>
         </is>
       </c>
-      <c r="C6" s="6">
+      <c r="C7" s="6">
         <v>46317</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="242" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光公告 9 月自結淨利 4.34 億元，3M 私募股款已匯入
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光 10 月 23 日公告自結 9 月歸屬母公司淨利約新台幣 4.34 億元，年減 15%，每股盈餘 3.85 元；同日媒體報導 3M 認購私募股款約 48.13 億元已匯入。雙方先前公布合作研發擴束光學（EBO）、共封裝光學與資料中心互連產品，但尚未公布量產客戶驗收或出貨量；股款入帳不等於新產品量產。玉晶光現有精密光學製造能力將支援 3M 的 EBO 光連接套管及光互連模組研製，供應鏈涉及精密材料、光學零組件、先進封裝與資料中心交換連接。自結損益反映既有業務，無法單獨歸因於尚未量產的光學互連合作。3M 10 月 19 日第一手公告稱擬取得玉晶光約 4.7% 股權，原計畫須完成慣例交割條件；10 月 23 日媒體說股款已匯入。玉晶光第三季營收約 78.12 億元、年增約 1%，歸屬母公司淨利約 10.92 億元、年減 23%，依中央社當日報導口徑，季度數字與單月不同。私募法律程序最終交割日、EBO 製造良率、客戶認證和出貨排程尚未完全披露；9 月及第三季損益屬公司自結。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C7" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="262" customHeight="1">
+    <row r="8" ht="294" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">06</t>
@@ -527,16 +531,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
+            <t xml:space="preserve">馬國總理披露 500 億美元 AI 與資料中心投資意向，未公告專案核准
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞總理安華 10 月 24 日在馬六甲表示，一名國際投資人於視訊會議中提出約 500 億美元的 AI、新科技與資料中心投資意向，地點包括砂拉越古晉及馬來西亞半島。新加坡《商業時報》10 月 25 日將投資人指為 SoftBank 創辦人孫正義，但尚無 SoftBank 正式投資承諾、核准專案、供電容量或動工日期公告。大型資料中心計畫涉及伺服器與機櫃 ODM、UPS 與電力轉換、冷卻設備、變電系統和光纖互連。安華亦談及半導體人才及向較高附加價值技術環節發展，但並未宣布半導體晶圓廠新案。馬來西亞國家通訊社 Bernama 記錄安華於 10 月 24 日公開發言，投資人意向來自前一週二的視訊會議。新加坡《商業時報》 25 日補充投資人姓名，並指 SoftBank 尚未回應置評要求；兩篇報導均未取得具體合約或許可文件。500 億美元是總理轉述的跨領域投資意向，沒有逐年撥款表、各州配置或已支付金額，不能計入核准 FDI、已建置機房容量或設備採購。投資人正式企業公告、土地權利、電網併接與需量、冷卻用水、專案融資、機房建照及交付時程尚未公布。地點：馬來西亞砂拉越州古晉及馬來西亞半島（擬投資地區，無已核實工地）；發言活動於馬六甲 Hang Jebat 運動場。</t>
           </r>
         </is>
       </c>
@@ -544,6 +548,117 @@
         <v>46319</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="242" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光公告 9 月自結淨利 4.34 億元，3M 私募股款已匯入
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光 10 月 23 日公告自結 9 月歸屬母公司淨利約新台幣 4.34 億元，年減 15%，每股盈餘 3.85 元；同日媒體報導 3M 認購私募股款約 48.13 億元已匯入。雙方先前公布合作研發擴束光學（EBO）、共封裝光學與資料中心互連產品，但尚未公布量產客戶驗收或出貨量；股款入帳不等於新產品量產。玉晶光現有精密光學製造能力將支援 3M 的 EBO 光連接套管及光互連模組研製，供應鏈涉及精密材料、光學零組件、先進封裝與資料中心交換連接。自結損益反映既有業務，無法單獨歸因於尚未量產的光學互連合作。3M 10 月 19 日第一手公告稱擬取得玉晶光約 4.7% 股權，原計畫須完成慣例交割條件；10 月 23 日媒體說股款已匯入。玉晶光第三季營收約 78.12 億元、年增約 1%，歸屬母公司淨利約 10.92 億元、年減 23%，依中央社當日報導口徑，季度數字與單月不同。私募法律程序最終交割日、EBO 製造良率、客戶認證和出貨排程尚未完全披露；9 月及第三季損益屬公司自結。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="6">
+        <v>46318</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="258" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">長榮航稱高科技空運需求持續，9 月貨運營收年增 42.55%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">長榮航空總經理孫嘉明 10 月 25 日在台北受訪表示，AI 伺服器及其他高科技貨運需求全年維持強勁，帶動運價，但航空燃油上漲仍是重要成本變數。公司先前公布的 9 月貨運營收為新台幣 61.67 億元、年增 42.55%，此為歷史月份實績，並非 10 月 25 日新增出貨量。航空貨運與台灣出口的 AI 伺服器、伺服器機櫃、半導體設備及高價值電子零組件有直接物流連結。不同貨型對載重、艙位、時效及地面操作要求不同，空運貨值與設備實際產能無法直接相比。長榮航管理階層 10 月 25 日表示航空油價曾達每桶約 177 美元，公司調整部分票價與運價，並指出高科技空運需求持續。9 月合併營收 207.49 億元、貨運營收 61.67 億元為先前公告實績，不能全部歸因於 AI 類貨物。貨運營收年增 42.55% 同時反映貨量、運價與運送組合，現有報導未提供分離量價因素的同期比較表。每桶 177 美元為受訪者引用的先前燃油水準，不是 10 月 25 日官方即時成交價格。未公布當日貨機裝載率、各類 AI 貨物實際噸數、客戶長約、燃油避險覆蓋或跨境專用運力新增合約。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="262" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="6">
+        <v>46319</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
         </is>

--- a/docs/exports/week-2026-10-25.xlsx
+++ b/docs/exports/week-2026-10-25.xlsx
@@ -134,21 +134,23 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">稀土材料與精密設備供應鏈
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">工研院 10 月 24 日表示，規劃 2028 年底完成稀土示範廠、2030 年達年產 500 噸，預期可滿足台灣約半數需求。建廠預算、地點及實際磁材產出尚未核定。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C3" s="6">
-        <v>46319</v>
+            <t xml:space="preserve">稀土、PCB 材料與新廠產能進度
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">工研院規劃稀土示範廠，仍待預算與廠址；騰輝 10 月 26 日在泰國大城府啟用 PCB 銅箔基板與黏合片工廠，並開始小量出貨。2030 年稀土目標與泰國廠年底量產均尚非實際產能。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/24、10/26</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="98" customHeight="1">
@@ -166,22 +168,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">颱風後供電復原與工廠電力、智慧系統
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">10 月 24 日台電通報全台累計逾 34 萬戶曾停電，宜蘭區處於 25 日宣布下午 4 時完成逾 3 萬受災民生用戶復電；各項數字分屬不同時點和地區，尚無半導體工廠停機資料。中華電信另公布智慧影像子公司成立，未揭露工業端裝機量。</t>
+            <t xml:space="preserve">工廠電力復原、AI 自動化與精密設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台電於 10 月 25 日公布宜蘭復電進度，沒有晶圓廠停機損失資料；鴻海與 NVIDIA 26 日公布特定工廠排程工時降低 25% 的測試，JIMTOF 亦在東京開展，台灣公會表示 94 家廠商參展。各數值來自不同場景，不適合直接比較。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/25</t>
+          <t xml:space="preserve">10/22、10/24、10/25、10/26</t>
         </is>
       </c>
     </row>
@@ -200,22 +202,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">東南亞海纜招標與馬來西亞資料中心投資意向
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 海纜開發商提出約 4 億美元建置估算與 2028 年底啟用目標；馬來西亞總理 24 日另轉述 500 億美元 AI／資料中心投資意向，媒體 25 日指涉 SoftBank 孫正義。兩案均缺少實際施工、併網及完工驗證，且投資金額不可視為已支出。</t>
+            <t xml:space="preserve">東南亞海纜、機房投資意向及跨境供電
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">MViSTA 海纜仍在招標、馬國總理提出 500 億美元資料中心投資意向；新加坡 EMA 於 26 日有條件核准 1.3GW 跨國低碳電力輸入，預定 2035 年啟動。三項進展分別為規劃、意向與條件性核准，非已完成建設。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24</t>
+          <t xml:space="preserve">10/22、10/24、10/26</t>
         </is>
       </c>
     </row>
@@ -234,26 +236,26 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">台灣光互連合作與高科技設備物流
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光與 3M 的光互連合作尚未確認量產交付；長榮航總經理 10 月 25 日稱 AI 伺服器等高科技貨運需求持續，但也指出航空燃油成本壓力。長榮航 9 月貨運營收年增 42.55%，為已公布的歷史營收數據，沒有拆分 AI 貨物量價。</t>
+            <t xml:space="preserve">光互連、貨運與 SMT 設備事業結構
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光與 3M 的 EBO 光互連產品尚未公布量產驗收，長榮航管理層 25 日說明高科技貨運需求；Reuters 26 日則報導 ASMPT 的 SMT 設備業務潛在出售競標。已公開的上半年接單、九月營收和潛在交易估值屬不同口徑。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/23、10/25</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="82" customHeight="1">
+          <t xml:space="preserve">10/23、10/25、10/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="98" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
@@ -268,21 +270,23 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">台菲半導體合作方向與 2030 年出口目標
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">駐菲代表 10 月 24 日在馬卡蒂市提及串聯台菲與呂宋經濟走廊的可能性，並引用菲律賓 2030 年電子與半導體產品年出口 1,100 億美元目標。現階段未公告新的半導體工廠核定投資。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C7" s="6">
-        <v>46319</v>
+            <t xml:space="preserve">東南亞晶圓製造及半導體合作
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">駐菲代表提出台菲半導體走廊合作方向，並引述 2030 年電子出口目標；Reuters 26 日實地報導 Viettel 越南晶圓廠仍無建築、DUV 設備未成交，但 Viettel 表示按階段推進。兩國均未在本週披露新晶圓廠已完成裝機。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/24、10/26</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -368,7 +372,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="246" customHeight="1">
+    <row r="4" ht="178" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02</t>
@@ -383,6 +387,43 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">騰輝泰國 PCB 材料新廠啟用並小量出貨，年底量產為目標
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">騰輝電子 10 月 26 日在泰國大城府 Hi-Tech 工業園區啟用占地約 3.5 萬平方公尺的銅箔基板與黏合片工廠，已小量出貨。公司預計 2026 年底量產，2027 年增加上膠設備後，總設計產能目標再增加 15%，但絕對產量尚未公布。銅箔基板與黏合片為多層 PCB、伺服器板件與汽車電子的上游材料，泰國廠是集團首座東南亞生產基地。啟用並小量出貨不等於已達量產良率。公司另提及 9 月核准的昆山廠 15 億元擴產計畫，該預算是既有中國工廠投資，不應計入本次泰國新廠資本支出。泰國建廠投入金額、月出貨量、良率及客戶認證進度未公布。地點：泰國大城府 Hi-Tech 工業園區（正式啟用之生產工廠）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCB 製程電源與量測設備業者可核對上膠線規格、實際稼動率及客戶驗收時程。小量出貨不代表已完成全部設備認證，無法推算後續機台採購。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="246" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">薔琵颱風造成全台逾 34 萬戶曾停電，台電 10 月 24 日下午稱復電率逾 9 成
 </t>
           </r>
@@ -396,22 +437,22 @@
           </r>
         </is>
       </c>
-      <c r="C4" s="6">
+      <c r="C5" s="6">
         <v>46319</v>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對供電設備與工業電力品質業者，應區分配電故障與廠區內備援系統失效，確認鹽塵環境下的絕緣設計、UPS 或儲能切換與實際停電波形。缺少個別工廠測量記錄，無法推定設備停機或產能損失。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -433,22 +474,22 @@
           </r>
         </is>
       </c>
-      <c r="C5" s="6">
+      <c r="C6" s="6">
         <v>46317</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工業控制電源、工業視覺測試與邊緣運算硬體供應商可確認新公司實際採用的攝影機、伺服器及邊緣裝置規格與驗收條件。尚無部署數量及工廠應用簽約資訊。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="242" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="7" ht="242" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -470,22 +511,96 @@
           </r>
         </is>
       </c>
-      <c r="C6" s="6">
+      <c r="C7" s="6">
         <v>46320</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程電源、UPS 和廠務監控供應商可查明各廠是否有實際電壓驟降、儲能切換或異常警報。家庭戶數復電不揭露機台開機狀態，因此不能換算設備停產或備援採購。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="310" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="8" ht="146" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">鴻海與 NVIDIA 公布智慧工廠實測：排程工時減 25%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">鴻海與 NVIDIA 10 月 26 日公布特定智慧工廠流程數據，生產排程工時降低 25%，射出工程工作量降低 50%。DGX 平台的特定模型訓練速度為既有 H100 系統的 2.48 倍，尚未提供跨廠驗證。製造應用涵蓋 SMT、排程、自動化、工業量測與伺服器 AI 訓練平台。NVIDIA 指出測試以既有 H100 平台為比較基準，且 12 天處理 1 兆 Token；流程改善數據不可視為整體工廠平均成效。受測廠區、絕對工時及產線良率比較資料未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製程量測與工業電源供應商可核對導入範圍及基準工時。缺乏跨廠數據，尚無法推定全面效益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="146" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">JIMTOF 東京開展，公會表示有 94 家台灣廠商參展
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">日本工具機展 JIMTOF 於 10 月 26 日在東京國際展示場開展，展期至 31 日。台灣工具機公會稱有 94 家台廠參展，包含 CNC、量測與工廠自動化設備；實際成交額及設備訂單未公布。精密加工及控制設備涉及工廠自動化與半導體設備零組件製造，展出不等於簽單。主辦方確認 10 月 26 至 31 日於 Tokyo Big Sight 舉行；公會參展家數由中央社轉述。展後成交、客戶驗證及設備採購量尚未公布。地點：日本東京 Tokyo Big Sight（實際展覽場館）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設備電源與精密量測業者可核實展出技術規格與客戶驗收情況。參展家數不代表新設備訂單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="310" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -507,22 +622,22 @@
           </r>
         </is>
       </c>
-      <c r="C7" s="6">
+      <c r="C10" s="6">
         <v>46317</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="294" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+    <row r="11" ht="294" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -541,117 +656,6 @@
               <color rgb="FF3B4A44"/>
             </rPr>
             <t xml:space="preserve">馬來西亞總理安華 10 月 24 日在馬六甲表示，一名國際投資人於視訊會議中提出約 500 億美元的 AI、新科技與資料中心投資意向，地點包括砂拉越古晉及馬來西亞半島。新加坡《商業時報》10 月 25 日將投資人指為 SoftBank 創辦人孫正義，但尚無 SoftBank 正式投資承諾、核准專案、供電容量或動工日期公告。大型資料中心計畫涉及伺服器與機櫃 ODM、UPS 與電力轉換、冷卻設備、變電系統和光纖互連。安華亦談及半導體人才及向較高附加價值技術環節發展，但並未宣布半導體晶圓廠新案。馬來西亞國家通訊社 Bernama 記錄安華於 10 月 24 日公開發言，投資人意向來自前一週二的視訊會議。新加坡《商業時報》 25 日補充投資人姓名，並指 SoftBank 尚未回應置評要求；兩篇報導均未取得具體合約或許可文件。500 億美元是總理轉述的跨領域投資意向，沒有逐年撥款表、各州配置或已支付金額，不能計入核准 FDI、已建置機房容量或設備採購。投資人正式企業公告、土地權利、電網併接與需量、冷卻用水、專案融資、機房建照及交付時程尚未公布。地點：馬來西亞砂拉越州古晉及馬來西亞半島（擬投資地區，無已核實工地）；發言活動於馬六甲 Hang Jebat 運動場。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C8" s="6">
-        <v>46319</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="242" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光公告 9 月自結淨利 4.34 億元，3M 私募股款已匯入
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光 10 月 23 日公告自結 9 月歸屬母公司淨利約新台幣 4.34 億元，年減 15%，每股盈餘 3.85 元；同日媒體報導 3M 認購私募股款約 48.13 億元已匯入。雙方先前公布合作研發擴束光學（EBO）、共封裝光學與資料中心互連產品，但尚未公布量產客戶驗收或出貨量；股款入帳不等於新產品量產。玉晶光現有精密光學製造能力將支援 3M 的 EBO 光連接套管及光互連模組研製，供應鏈涉及精密材料、光學零組件、先進封裝與資料中心交換連接。自結損益反映既有業務，無法單獨歸因於尚未量產的光學互連合作。3M 10 月 19 日第一手公告稱擬取得玉晶光約 4.7% 股權，原計畫須完成慣例交割條件；10 月 23 日媒體說股款已匯入。玉晶光第三季營收約 78.12 億元、年增約 1%，歸屬母公司淨利約 10.92 億元、年減 23%，依中央社當日報導口徑，季度數字與單月不同。私募法律程序最終交割日、EBO 製造良率、客戶認證和出貨排程尚未完全披露；9 月及第三季損益屬公司自結。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C9" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="258" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">長榮航稱高科技空運需求持續，9 月貨運營收年增 42.55%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">長榮航空總經理孫嘉明 10 月 25 日在台北受訪表示，AI 伺服器及其他高科技貨運需求全年維持強勁，帶動運價，但航空燃油上漲仍是重要成本變數。公司先前公布的 9 月貨運營收為新台幣 61.67 億元、年增 42.55%，此為歷史月份實績，並非 10 月 25 日新增出貨量。航空貨運與台灣出口的 AI 伺服器、伺服器機櫃、半導體設備及高價值電子零組件有直接物流連結。不同貨型對載重、艙位、時效及地面操作要求不同，空運貨值與設備實際產能無法直接相比。長榮航管理階層 10 月 25 日表示航空油價曾達每桶約 177 美元，公司調整部分票價與運價，並指出高科技空運需求持續。9 月合併營收 207.49 億元、貨運營收 61.67 億元為先前公告實績，不能全部歸因於 AI 類貨物。貨運營收年增 42.55% 同時反映貨量、運價與運送組合，現有報導未提供分離量價因素的同期比較表。每桶 177 美元為受訪者引用的先前燃油水準，不是 10 月 25 日官方即時成交價格。未公布當日貨機裝載率、各類 AI 貨物實際噸數、客戶長約、燃油避險覆蓋或跨境專用運力新增合約。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C10" s="6">
-        <v>46320</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="262" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
           </r>
         </is>
       </c>
@@ -660,7 +664,229 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="162" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">新加坡有條件核准跨境進口電力 1.3GW，目標 2035 年開始供應
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">EMA 於 10 月 26 日有條件核准 Sembcorp Utilities 輸入最多 1.3GW 低碳電力，規劃由越南與馬來西亞供應新加坡，目標 2035 年供電。計畫包含越南離岸風電及馬國太陽能與儲能，但仍待多國許可、購電協議及融資。跨國電力走廊涉及輸變電、電源轉換、儲能及資料中心供電。1.3GW 是有條件核准額度，並非實際併網或發電容量。參與企業包括 Petronas、TNB 及越南 PTSC，早於 2025 年 5 月簽訂共同開發協議。10 月 26 日新增條件性核准，後續還須完成跨境許可與融資。實際線路場址、建設經費、購電價格與正式併網時程尚未確定。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電力轉換與機房供電設備業者可核對輸配電規格、電池配置及購電合約。尚無施工與融資定案資料，無法推估供應商設備交付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="242" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光公告 9 月自結淨利 4.34 億元，3M 私募股款已匯入
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光 10 月 23 日公告自結 9 月歸屬母公司淨利約新台幣 4.34 億元，年減 15%，每股盈餘 3.85 元；同日媒體報導 3M 認購私募股款約 48.13 億元已匯入。雙方先前公布合作研發擴束光學（EBO）、共封裝光學與資料中心互連產品，但尚未公布量產客戶驗收或出貨量；股款入帳不等於新產品量產。玉晶光現有精密光學製造能力將支援 3M 的 EBO 光連接套管及光互連模組研製，供應鏈涉及精密材料、光學零組件、先進封裝與資料中心交換連接。自結損益反映既有業務，無法單獨歸因於尚未量產的光學互連合作。3M 10 月 19 日第一手公告稱擬取得玉晶光約 4.7% 股權，原計畫須完成慣例交割條件；10 月 23 日媒體說股款已匯入。玉晶光第三季營收約 78.12 億元、年增約 1%，歸屬母公司淨利約 10.92 億元、年減 23%，依中央社當日報導口徑，季度數字與單月不同。私募法律程序最終交割日、EBO 製造良率、客戶認證和出貨排程尚未完全披露；9 月及第三季損益屬公司自結。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="6">
+        <v>46318</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="258" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">長榮航稱高科技空運需求持續，9 月貨運營收年增 42.55%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">長榮航空總經理孫嘉明 10 月 25 日在台北受訪表示，AI 伺服器及其他高科技貨運需求全年維持強勁，帶動運價，但航空燃油上漲仍是重要成本變數。公司先前公布的 9 月貨運營收為新台幣 61.67 億元、年增 42.55%，此為歷史月份實績，並非 10 月 25 日新增出貨量。航空貨運與台灣出口的 AI 伺服器、伺服器機櫃、半導體設備及高價值電子零組件有直接物流連結。不同貨型對載重、艙位、時效及地面操作要求不同，空運貨值與設備實際產能無法直接相比。長榮航管理階層 10 月 25 日表示航空油價曾達每桶約 177 美元，公司調整部分票價與運價，並指出高科技空運需求持續。9 月合併營收 207.49 億元、貨運營收 61.67 億元為先前公告實績，不能全部歸因於 AI 類貨物。貨運營收年增 42.55% 同時反映貨量、運價與運送組合，現有報導未提供分離量價因素的同期比較表。每桶 177 美元為受訪者引用的先前燃油水準，不是 10 月 25 日官方即時成交價格。未公布當日貨機裝載率、各類 AI 貨物實際噸數、客戶長約、燃油避險覆蓋或跨境專用運力新增合約。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="214" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">Reuters：ASMPT 的 SMT 業務出售仍在競標，尚無完成交易
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">Reuters 10 月 26 日引述匿名人士稱，IDG Capital 在新加坡總部 ASMPT 的 SMT 事業洽購中較為領先，潛在交易價值可能逾 10 億美元，但尚未定案。ASMPT 於 2026 年 1 月啟動策略檢視，原始公告列出售、合資、分拆、上市或保留等多種選項。SMT 設備涉及電子板件印刷、貼片、檢測及產線軟體，應用於 AI 伺服器、光收發器及汽車電子組裝。競標報導尚不能證明設備支援與保固安排將改變。Reuters 引述上半年業務數據：SMT 營收年增 53.1% 至 38.7 億港元，接單年增 87.8% 至 69.8 億港元。上述為上半年歷史實績，新消息僅是洽購進度。未簽正式出售合約，買方、價金、監管申報及員工安排均未證實。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C15" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMT 電源、測試及設備服務供應商可追蹤正式買方與保固責任是否變更。未有已簽合約，不應推定採購或客戶合約轉移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="262" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C16" s="6">
+        <v>46319</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="246" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">Reuters：越南 Viettel 晶圓廠尚無廠房，DUV 設備採購未定案
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">Reuters 10 月 26 日報導，越南 Viettel 在河內近郊規劃的首座晶圓廠，自 1 月動土以來尚未建起廠房，與 ASML 的 DUV 曝光機洽談亦未成交。知情人士認為 2027 年試產可能延後，但 Viettel 表示計畫仍依階段推進；目前沒有一致確認的新試產日期。越南已有 Intel、Amkor、Hana Micron 等封裝測試基地，Viettel 計畫進入前段晶圓製造，將涉及微影、沉積、蝕刻、製程電源與無塵室設施。封測產能不能替代前段晶圓廠建設。Reuters 實地查訪與衛星影像指出仍無建築，並報導越南當局先前估算建廠約 13 億美元、原定 2027 年試產及 2030 年全面運作。Viettel 回應計畫按階段推進，ASML 未確認設備合約。DUV 型號、正式採購合約、施工許可、製程技轉方及可查證的試產日期均未公布。地點：越南河內近郊 Viettel 規劃晶圓廠基地（確切工業區未披露）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C17" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源、量測與廠務設備業者可追問正式機台採購、技術合約與開工許可。現地觀察和業者回覆存在差異，不能把 2027 年當作已確認的量產日期。</t>
         </is>
       </c>
     </row>

--- a/docs/exports/week-2026-10-25.xlsx
+++ b/docs/exports/week-2026-10-25.xlsx
@@ -134,22 +134,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">稀土、PCB 材料與新廠產能進度
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">工研院規劃稀土示範廠，仍待預算與廠址；騰輝 10 月 26 日在泰國大城府啟用 PCB 銅箔基板與黏合片工廠，並開始小量出貨。2030 年稀土目標與泰國廠年底量產均尚非實際產能。</t>
+            <t xml:space="preserve">記憶體、電子材料與稀土供應
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">工研院規劃稀土示範廠，騰輝在泰國啟用銅箔基板廠，旺宏說明新增 NAND／eMMC 產能預計 2027 年下半年開出；晶豪科則公布第三季記憶體財務實績。上述資訊分別屬未來目標、已啟用廠房與已認列收入。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/24、10/26</t>
+          <t xml:space="preserve">10/24、10/26、10/27</t>
         </is>
       </c>
     </row>
@@ -168,22 +168,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">工廠電力復原、AI 自動化與精密設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台電於 10 月 25 日公布宜蘭復電進度，沒有晶圓廠停機損失資料；鴻海與 NVIDIA 26 日公布特定工廠排程工時降低 25% 的測試，JIMTOF 亦在東京開展，台灣公會表示 94 家廠商參展。各數值來自不同場景，不適合直接比較。</t>
+            <t xml:space="preserve">工廠設備、製程量測與自動化
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台電公布颱風復電進度，鴻海與 NVIDIA 報告特定流程效率，中華電信成立智慧影像子公司；國研院與汎銓公布 High-NA EUV 樣品檢測方法，宏偉聲稱特殊工業電梯訂單能見度達三年。製造效率、技術開發與接單指標不能等量比較。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/25、10/26</t>
+          <t xml:space="preserve">10/22、10/24、10/25、10/26、10/27</t>
         </is>
       </c>
     </row>
@@ -202,22 +202,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">東南亞海纜、機房投資意向及跨境供電
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 海纜仍在招標、馬國總理提出 500 億美元資料中心投資意向；新加坡 EMA 於 26 日有條件核准 1.3GW 跨國低碳電力輸入，預定 2035 年啟動。三項進展分別為規劃、意向與條件性核准，非已完成建設。</t>
+            <t xml:space="preserve">東南亞電源與資料中心基礎設施
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">MViSTA 海纜仍在供應商招標，馬來西亞總理談及大型資料中心投資意向，新加坡 EMA 另有條件核准 1.3GW 跨境電力計畫；台達電泰國子公司公告向集團新加坡公司取得設備。跨境電力核准、投資意向及關係人資產取得都不能視為已裝機容量。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/26</t>
+          <t xml:space="preserve">10/22、10/24、10/26、10/27</t>
         </is>
       </c>
     </row>
@@ -236,22 +236,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">光互連、貨運與 SMT 設備事業結構
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光與 3M 的 EBO 光互連產品尚未公布量產驗收，長榮航管理層 25 日說明高科技貨運需求；Reuters 26 日則報導 ASMPT 的 SMT 設備業務潛在出售競標。已公開的上半年接單、九月營收和潛在交易估值屬不同口徑。</t>
+            <t xml:space="preserve">封裝測試、光互連與高科技設備供應
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光與 3M 光互連合作尚無已驗收量產數據，長榮航說明高科技貨運需求，ASMPT 的 SMT 事業出售仍在洽談；力成新公布先進封裝營收占比逾三成，中華精測公布晶圓測試卡帶動的第三季實績。FOPLP 的 2027 年量產目標仍與現有封測收入分開。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/23、10/25、10/26</t>
+          <t xml:space="preserve">10/23、10/25、10/26、10/27</t>
         </is>
       </c>
     </row>
@@ -270,22 +270,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">東南亞晶圓製造及半導體合作
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">駐菲代表提出台菲半導體走廊合作方向，並引述 2030 年電子出口目標；Reuters 26 日實地報導 Viettel 越南晶圓廠仍無建築、DUV 設備未成交，但 Viettel 表示按階段推進。兩國均未在本週披露新晶圓廠已完成裝機。</t>
+            <t xml:space="preserve">晶圓設計、製造專案與跨境合作
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台菲經濟走廊合作仍屬政策方向，Reuters 指越南 Viettel 晶圓廠工程與 DUV 採購未完成；智原 10 月 27 日公布與三星及聯電相關的美國 2 奈米 GAA 設計案。晶片委託設計、晶圓廠建造與量產出貨是不同執行階段。</t>
           </r>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/24、10/26</t>
+          <t xml:space="preserve">10/24、10/26、10/27</t>
         </is>
       </c>
     </row>
@@ -409,7 +409,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="246" customHeight="1">
+    <row r="5" ht="198" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">03</t>
@@ -424,6 +424,80 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">旺宏第三季營收 242.37 億元，新 NAND／eMMC 產能估 2027 下半年投入
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">旺宏 10 月 27 日法說公布第三季營收 242.37 億元、毛利率 70.5%、淨利 109.51 億元。公司表示今年投資超過 300 億元，新增產能須待 2027 年下半年逐步產出，將以 NAND Flash 與 eMMC 為主；NOR Flash 不再擴充，並逐步淡出 ROM。旺宏的 NOR、NAND、eMMC 供應工業控制、車載電子及儲存等不同用途，新增產能規劃與本季因價格及產品組合變動的營收，須區分不同驅動因素。董事長指出新建產能須超過一年才能產出，短期收入提升主要來自價格變化，並未披露新增晶圓月投片數或取得的實際設備交貨。新產線廠區配置、實際 NAND／eMMC 投片規模、良率及訂單數量未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記憶體製程電源與量測設備供應商會先核對新增 NAND 晶圓線的實際機台交期、投片及測試規格。公司所述的未來產出時間並不能證明現有採購已完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="198" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">晶豪科第三季營收 221.5 億元、歸母淨利 107.59 億元，毛利率 77.44%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">晶豪科 10 月 27 日公告第三季營收 221.5 億元、毛利率 77.44%、歸母淨利 107.59 億元與每股純益 36.79 元。公司報告營收季增 58.8%、淨利季增約 82%，但漲價及產品組合因素未附完整量價拆解，不能將收入成長當成晶圓產量成長。晶豪科提供各類記憶體晶片與控制用途元件，記憶體市場價格變化對其毛利率與營收具有影響；本期公司財務數據無法直接代表 NAND、DRAM 或其他品類個別量產增幅。第三季毛利率較第二季增加 8.74 個百分點。累計前九月營收 433.63 億元、歸母淨利 187.3 億元，是前三季累計，不能與單季同列比較。未取得公司原始正式財報、產品分項出貨量、價格與銷量的個別變動。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記憶體製程電源與測試設備業者應確認產品組合、實際投片與封測產能利用率是否有相對應的實績。營收大幅上升不能直接證明設備新增訂單或晶圓出貨同幅成長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="246" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">薔琵颱風造成全台逾 34 萬戶曾停電，台電 10 月 24 日下午稱復電率逾 9 成
 </t>
           </r>
@@ -437,22 +511,22 @@
           </r>
         </is>
       </c>
-      <c r="C5" s="6">
+      <c r="C7" s="6">
         <v>46319</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對供電設備與工業電力品質業者，應區分配電故障與廠區內備援系統失效，確認鹽塵環境下的絕緣設計、UPS 或儲能切換與實際停電波形。缺少個別工廠測量記錄，無法推定設備停機或產能損失。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="8" ht="178" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -474,22 +548,22 @@
           </r>
         </is>
       </c>
-      <c r="C6" s="6">
+      <c r="C8" s="6">
         <v>46317</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工業控制電源、工業視覺測試與邊緣運算硬體供應商可確認新公司實際採用的攝影機、伺服器及邊緣裝置規格與驗收條件。尚無部署數量及工廠應用簽約資訊。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="242" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="9" ht="242" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -511,22 +585,22 @@
           </r>
         </is>
       </c>
-      <c r="C7" s="6">
+      <c r="C9" s="6">
         <v>46320</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程電源、UPS 和廠務監控供應商可查明各廠是否有實際電壓驟降、儲能切換或異常警報。家庭戶數復電不揭露機台開機狀態，因此不能換算設備停產或備援採購。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="146" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+    <row r="10" ht="146" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -548,22 +622,22 @@
           </r>
         </is>
       </c>
-      <c r="C8" s="6">
+      <c r="C10" s="6">
         <v>46321</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程量測與工業電源供應商可核對導入範圍及基準工時。缺乏跨廠數據，尚無法推定全面效益。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="146" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+    <row r="11" ht="146" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -585,22 +659,96 @@
           </r>
         </is>
       </c>
-      <c r="C9" s="6">
+      <c r="C11" s="6">
         <v>46321</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">設備電源與精密量測業者可核實展出技術規格與客戶驗收情況。參展家數不代表新設備訂單。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="310" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+    <row r="12" ht="178" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">國研院與汎銓公布 High-NA EUV 光阻奈米結構鍍膜檢測技術
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">國研院 10 月 27 日宣布，國儀中心與汎銓合作，在 High-NA EUV 與金屬氧化物光阻（MOR）曝光後，以鍍膜強化奈米結構，支援後續晶圓剖面分析。國研院稱技術已協助汎銓進入大型半導體設備與製造商供應鏈，但未公布已完成驗收的客戶、良率或量產導入規模。在高數值孔徑 EUV 微影後，金屬氧化物光阻形成的微細結構在斷面檢測前須保持形狀。樣品製備與量測結果涉及先進晶圓製程、材料分析及電子顯微技術。國研院指出，以專用鍍膜輔助強化脆弱奈米結構後，可提供後續檢測分析；公開的是研究技術突破，並未表示某製程節點已進入高良率量產。未披露可比較的缺陷率、解析度實驗結果、半導體廠認證時程及商用檢測設備採購量。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製程量測、電源及分析設備業者可檢查不同光阻與膜層的適用範圍、樣品重現性及實際客戶驗證程序。研究成功不代表已取得量產設備合約。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="178" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">宏偉電機稱高載重及無塵室工業電梯訂單能見度達三年
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">宏偉電機 10 月 27 日媒體交流會指出，高載重、無塵室與自動搬運用途電梯的在手訂單能見度延長至三年，今年在手訂單數量較 2025 年增加一倍。公司說半導體周邊相關出貨占比約 59%，客戶涵蓋晶圓、封測與高科技工廠，但未公布可供核對的訂單絕對金額或特定廠房。高載重、無塵室與防爆電梯可用於晶圓、封測和精密工廠的物流與廠務動線。這類建廠周邊設備不等同於曝光、蝕刻或封測機台本身。公司說今年接單出貨比持續逾一，業務涵蓋晶圓代工、半導體設備及後段封測客戶；在手訂單三年是企業口徑，並非確定三年營收額。沒有完整訂單台數、金額、交貨表、最終工地與客戶名稱，亦無可獨立驗證的在手訂單明細。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工廠電力與自動搬運設備業者可核對實際交付工地、升降設備負載規格及施工驗收。訂單能見度不是已實現營收，也不能用來推估任何晶圓廠的投產日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="310" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -622,22 +770,22 @@
           </r>
         </is>
       </c>
-      <c r="C10" s="6">
+      <c r="C14" s="6">
         <v>46317</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="294" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="15" ht="294" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -659,22 +807,22 @@
           </r>
         </is>
       </c>
-      <c r="C11" s="6">
+      <c r="C15" s="6">
         <v>46319</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="162" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="16" ht="162" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -696,22 +844,59 @@
           </r>
         </is>
       </c>
-      <c r="C12" s="6">
+      <c r="C16" s="6">
         <v>46321</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">電力轉換與機房供電設備業者可核對輸配電規格、電池配置及購電合約。尚無施工與融資定案資料，無法推估供應商設備交付。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="242" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="17" ht="194" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">台達電泰國子公司擬取得 3,450 萬美元設備，賣方為集團新加坡公司
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台達電 10 月 27 日代泰國子公司 DET 公告，董事會決議向同集團新加坡子公司 DEIL-SG 取得供營業使用設備，總交易金額約 3,450 萬美元，說明與轉型智慧工廠的製造策略有關。此為關係人間設備資產交易，不等同於新增跨境外商投資或設備已全部驗收。設備轉移可能涉及產線自動化、產能配置與集團廠區間資產管理；公告僅以『供營業使用設備』描述，未提供品項和製造線別。中央社引述上市公司 10 月 27 日重大訊息，交易由 DET 董事會決議，對手方為台達電新加坡子公司，交易金額約美金 3,450 萬。公告列明議價及電匯，不是新加坡外部企業對泰國的新股權投資。設備清單、所在廠址、原值、安裝時程、產能變動與實際付款日期未公布。地點：泰國 DET 子公司（實際設備裝設廠址未公告）；交易相對方位於新加坡。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C17" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">智慧工廠電源、控制與測試系統業者可核對移轉設備類別、既有與新增裝機占比以及驗收階段。關係人交易價值不等於泰國廠新增加的生產能力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="242" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -733,22 +918,22 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="6">
+      <c r="C18" s="6">
         <v>46318</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="258" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="19" ht="258" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -770,22 +955,22 @@
           </r>
         </is>
       </c>
-      <c r="C14" s="6">
+      <c r="C19" s="6">
         <v>46320</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="214" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="20" ht="214" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -807,22 +992,96 @@
           </r>
         </is>
       </c>
-      <c r="C15" s="6">
+      <c r="C20" s="6">
         <v>46321</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">SMT 電源、測試及設備服務供應商可追蹤正式買方與保固責任是否變更。未有已簽合約，不應推定採購或客戶合約轉移。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="262" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="21" ht="194" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">力成先進封裝營收占比逾三成，第三季封測稼動率逾九成
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">力成 10 月 27 日法說公布第三季營收 253.34 億元、毛利率 24%、歸母淨利 26.12 億元；公司稱先進封裝營收占比已逾三成，第三季封裝與測試產能利用率逾九成。FOPLP 客戶驗證仍在進行，2027 年量產及新加坡投資進度均尚未確定完成。公司業務涵蓋 DRAM、NAND／eSSD 與邏輯封測，新規劃包含 FOPLP、FCBGA、2.5D／3D 異質整合及 CPO 光學引擎。這些製程分屬不同封裝產品，不應合併為已量產的同一產能。公司稱第三季大型晶片 FCBGA 已導入量產，第四季規劃更大尺寸；FOPLP 仍為 2027 年量產目標。董事長表示不排除與晶圓廠合作，但尚無正式策略聯盟合約。FOPLP 客戶認證、絕對月產能、新加坡投資金額與實際交付時點未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C21" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先進封裝設備、測試電源及量測介面供應商需要確認 FOPLP 與高階 FCBGA 實際通過客戶認證的封裝尺寸、產線設備要求及交付里程碑。第三季稼動率與 2027 年擴產計畫屬不同時點，不能直接換算設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="198" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">中華精測第三季營收 19.05 億元、淨利 5.51 億元，晶圓測試卡占前九月營收 71%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">中華精測 10 月 27 日董事會通過第三季營運成果，合併營收新台幣 19.05 億元，年增 53.4%，歸母淨利 5.51 億元，年增 100%。公司指出前九月晶圓測試卡占營收 71%、IC 測試板 21%，但下一代探針卡的個別客戶認證及產能尚未公布。晶圓探針卡、IC 測試板與高頻高速測試介面連結記憶體、AI ASIC 及先進晶圓製程的晶圓電測和後段測試。產品營收占比並非絕對生產片數。公司第一手報告另列第三季毛利率 57.3%、營業利益率約 35%，且提及 AI 客製晶片相關測試介面需求。第三季營收及獲利的 YoY 基期未於該新聞稿列同口徑絕對金額。未公布下一代探針卡客戶清單、產能稼動、產品認證周期與實際新增機台投資。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C22" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高頻測試電源與探針卡設備業者可核對實際驗證通道、訊號與電源完整性標準，以及下一代測試卡的客戶接受節點。營收結構不能直接換算設備採購或實際測試吞吐量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="262" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -844,22 +1103,22 @@
           </r>
         </is>
       </c>
-      <c r="C16" s="6">
+      <c r="C23" s="6">
         <v>46319</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="246" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="24" ht="246" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -881,12 +1140,49 @@
           </r>
         </is>
       </c>
-      <c r="C17" s="6">
+      <c r="C24" s="6">
         <v>46321</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">晶圓製程電源、量測與廠務設備業者可追問正式機台採購、技術合約與開工許可。現地觀察和業者回覆存在差異，不能把 2027 年當作已確認的量產日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="198" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">智原取得三星 2 奈米 GAA 雲端晶片設計專案，明年上半年擬認列收入
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">智原 10 月 27 日於法說會表示，與三星晶圓代工、聯電及記憶體供應商合作，取得美國客戶 2 奈米 GAA 雲端 AI 晶片 NRE 專案，金額為數千萬美元。公司預估 2027 年上半年開始認列首筆設計收入，但未公布精確訂單價值、客戶及晶片量產驗證日期。NRE 專案涵蓋先進製程晶片設計及多廠協作；使用三星 2 奈米代工與聯電合作，不等於聯電已可製造 2 奈米晶圓。公司第三季營收 36.64 億元，毛利率 42.5%，歸母淨利 2.79 億元；管理階層說明量產產品比重上升影響毛利率，業外評價利益亦影響淨利成長。未知客戶、製程封裝、NRE 收入精確排程及客戶晶片實際出貨量。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源與先進封裝測試業者會確認實際代工場、封裝介面、矽智財驗證及後續晶片試產時程。專案 NRE 金額並非晶圓代工或設備採購支出。</t>
         </is>
       </c>
     </row>

--- a/docs/exports/week-2026-10-25.xlsx
+++ b/docs/exports/week-2026-10-25.xlsx
@@ -119,7 +119,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="82" customHeight="1">
+    <row r="3" ht="98" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">01</t>
@@ -134,22 +134,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">記憶體、電子材料與稀土供應
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">工研院規劃稀土示範廠，騰輝在泰國啟用銅箔基板廠，旺宏說明新增 NAND／eMMC 產能預計 2027 年下半年開出；晶豪科則公布第三季記憶體財務實績。上述資訊分別屬未來目標、已啟用廠房與已認列收入。</t>
+            <t xml:space="preserve">記憶體模組、材料與高速晶片供應
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">工研院提出稀土材料規劃、騰輝泰國銅箔基板廠已小量出貨，旺宏記憶體擴產仍待 2027 年開出。十銓 10 月 28 日提出新北模組廠 2027 年第二季投產目標；譜瑞則預估第四季高速介面晶片營收季減，這些數字分屬實際、規劃及財測。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/24、10/26、10/27</t>
+          <t xml:space="preserve">10/24、10/26、10/27、10/28</t>
         </is>
       </c>
     </row>
@@ -168,22 +168,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">工廠設備、製程量測與自動化
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台電公布颱風復電進度，鴻海與 NVIDIA 報告特定流程效率，中華電信成立智慧影像子公司；國研院與汎銓公布 High-NA EUV 樣品檢測方法，宏偉聲稱特殊工業電梯訂單能見度達三年。製造效率、技術開發與接單指標不能等量比較。</t>
+            <t xml:space="preserve">晶圓測試、工廠自動化與精密設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">颱風後電網復原與鴻海 AI 工廠效率資料各屬不同營運場景；國研院與汎銓發表 High-NA EUV 樣品分析方法。中華精測 10 月 28 日新增探針卡營收與 2027 年產能目標，金鞍機械龍潭廠正式啟用，兩案仍有待確認絕對產能與交付。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/25、10/26、10/27</t>
+          <t xml:space="preserve">10/22、10/24、10/25、10/26、10/27、10/28</t>
         </is>
       </c>
     </row>
@@ -202,22 +202,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">東南亞電源與資料中心基礎設施
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 海纜仍在供應商招標，馬來西亞總理談及大型資料中心投資意向，新加坡 EMA 另有條件核准 1.3GW 跨境電力計畫；台達電泰國子公司公告向集團新加坡公司取得設備。跨境電力核准、投資意向及關係人資產取得都不能視為已裝機容量。</t>
+            <t xml:space="preserve">台灣與東南亞資料中心電力及供應鏈
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">MViSTA 海纜仍在招標，馬來西亞 500 億美元資料中心投資意向未具正式專案核准；新加坡跨國電力輸入取得條件性核准。台達電公布第三季合併財報，是方電訊報告機房業績與 LY2 進駐率目標；各案的財務實績、投資意向及已併網容量不可混為一談。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/26、10/27</t>
+          <t xml:space="preserve">10/22、10/24、10/26、10/27、10/28</t>
         </is>
       </c>
     </row>
@@ -236,26 +236,26 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">封裝測試、光互連與高科技設備供應
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光與 3M 光互連合作尚無已驗收量產數據，長榮航說明高科技貨運需求，ASMPT 的 SMT 事業出售仍在洽談；力成新公布先進封裝營收占比逾三成，中華精測公布晶圓測試卡帶動的第三季實績。FOPLP 的 2027 年量產目標仍與現有封測收入分開。</t>
+            <t xml:space="preserve">先進封裝、光通訊與電子測試設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光與 3M 光互連合作尚未公布量產客戶驗收；力成先進封裝營收占比已逾三成，FOPLP 仍待量產認證。ASMPT SMT 交易仍屬未簽約洽談，穩懋 10 月 28 日公布光接收 PD 產能爬坡與第三季財報，不能將遠期出貨目標視為已交付。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/23、10/25、10/26、10/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98" customHeight="1">
+          <t xml:space="preserve">10/23、10/25、10/26、10/27、10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="114" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
@@ -270,22 +270,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">晶圓設計、製造專案與跨境合作
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台菲經濟走廊合作仍屬政策方向，Reuters 指越南 Viettel 晶圓廠工程與 DUV 採購未完成；智原 10 月 27 日公布與三星及聯電相關的美國 2 奈米 GAA 設計案。晶片委託設計、晶圓廠建造與量產出貨是不同執行階段。</t>
+            <t xml:space="preserve">晶圓製造、跨境合作及晶片監管
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台菲半導體經濟走廊仍為政策討論，Reuters 先前報導越南 Viettel 晶圓廠工地與 DUV 採購未完成，智原另宣布 2 奈米晶片委託設計案。聯電 10 月 28 日核准追加約 32 億美元擴產預算，馬來西亞海關同日公布 15 日查獲的 AI 晶片伺服器案件；核准資本支出與海關查扣均須保留其性質與日期。</t>
           </r>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/24、10/26、10/27</t>
+          <t xml:space="preserve">10/15、10/24、10/26、10/27、10/28</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="246" customHeight="1">
+    <row r="7" ht="214" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
@@ -498,6 +498,80 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">十銓在新北購置約 1,000 坪新廠，2027 年第二季規劃投產並增產能約 50%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">十銓 10 月 28 日公布，在新北市購置約 1,000 坪廠房，計畫於 2027 年第一季裝修及導入自動化設備、第二季投產，預估產能增加約 50%。第三季營收 101.39 億元、EPS 37.19 元；媒體同篇報導的第三季淨利金額出現前後不一致，因此暫不採用該數字。十銓從事 DRAM、SSD 等記憶體模組及企業與工控用儲存產品，新增工廠聚焦少量多樣的模組組裝與測試。模組產能與上游記憶體晶圓產能不可混為一談。公司亦整合 B2B 與 B2C 事業群，另購置約 700 坪辦公空間。50% 為公司預估的總產能增幅，但未提供目前月產量基準或設備投資額。新廠精確位置、契約金額、機台採購、合格模組產能及財報矛盾的單季淨利數值仍待查明。地點：台灣新北市（已購置廠房，未公開確切地址或工業區）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記憶體模組測試電源與工廠自動化設備業者需了解新廠的模組測試流程、稼動率基準及客戶認證需求。增產 50% 是規劃值，不能視為已完成的設備安裝量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="198" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">譜瑞預估第四季營收季減 20% 至 27%，高速介面晶片受 PC 零組件成本影響
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">譜瑞 10 月 28 日表示第四季營收估約 9,500 萬至 1.05 億美元，季減約 20% 至 27%；第三季營收約 1.3 億美元、毛利率 40.29%。公司指出 DRAM 及晶圓代工、後段封測漲價影響筆電需求與成本，預期第四季毛利率區間 41% 至 45% 為財測而非已實現結果。高速傳輸晶片用於筆記型電腦、顯示器與資料通道，供應鏈含晶圓代工及封裝測試。需求與定價受終端 PC、DRAM 及製造成本共同影響，不能單以記憶體價格解釋全部營收變化。公司表示上游代工與封測成本提高，將調整產品售價；第四季營收與毛利率皆為區間估計，沒有提供確認的客戶訂單數。未公布主要 PC 客戶訂單數、成本轉嫁比例及第四季已出貨產品組合。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源與測試設備業者會分辨高階介面晶片的現有出貨與尚未實現的季營收指引，確認實際需求及產品組合。售價與成本轉嫁仍需後續財報才能驗證。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="246" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">薔琵颱風造成全台逾 34 萬戶曾停電，台電 10 月 24 日下午稱復電率逾 9 成
 </t>
           </r>
@@ -511,22 +585,22 @@
           </r>
         </is>
       </c>
-      <c r="C7" s="6">
+      <c r="C9" s="6">
         <v>46319</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對供電設備與工業電力品質業者，應區分配電故障與廠區內備援系統失效，確認鹽塵環境下的絕緣設計、UPS 或儲能切換與實際停電波形。缺少個別工廠測量記錄，無法推定設備停機或產能損失。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="178" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+    <row r="10" ht="178" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -548,22 +622,22 @@
           </r>
         </is>
       </c>
-      <c r="C8" s="6">
+      <c r="C10" s="6">
         <v>46317</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工業控制電源、工業視覺測試與邊緣運算硬體供應商可確認新公司實際採用的攝影機、伺服器及邊緣裝置規格與驗收條件。尚無部署數量及工廠應用簽約資訊。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="242" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+    <row r="11" ht="242" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -585,22 +659,22 @@
           </r>
         </is>
       </c>
-      <c r="C9" s="6">
+      <c r="C11" s="6">
         <v>46320</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程電源、UPS 和廠務監控供應商可查明各廠是否有實際電壓驟降、儲能切換或異常警報。家庭戶數復電不揭露機台開機狀態，因此不能換算設備停產或備援採購。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="146" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+    <row r="12" ht="146" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -622,22 +696,22 @@
           </r>
         </is>
       </c>
-      <c r="C10" s="6">
+      <c r="C12" s="6">
         <v>46321</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程量測與工業電源供應商可核對導入範圍及基準工時。缺乏跨廠數據，尚無法推定全面效益。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="146" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="13" ht="146" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -659,22 +733,22 @@
           </r>
         </is>
       </c>
-      <c r="C11" s="6">
+      <c r="C13" s="6">
         <v>46321</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">設備電源與精密量測業者可核實展出技術規格與客戶驗收情況。參展家數不代表新設備訂單。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="178" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="14" ht="178" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -696,22 +770,22 @@
           </r>
         </is>
       </c>
-      <c r="C12" s="6">
+      <c r="C14" s="6">
         <v>46322</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程量測、電源及分析設備業者可檢查不同光阻與膜層的適用範圍、樣品重現性及實際客戶驗證程序。研究成功不代表已取得量產設備合約。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="178" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="15" ht="178" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -733,90 +807,16 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="6">
+      <c r="C15" s="6">
         <v>46322</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工廠電力與自動搬運設備業者可核對實際交付工地、升降設備負載規格及施工驗收。訂單能見度不是已實現營收，也不能用來推估任何晶圓廠的投產日期。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="310" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 海纜開發商稱將於 10 月決標，規劃串聯東南亞四國與越南資料中心
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">Reuters 10 月 22 日引述越南 Stavian 旗下 MViSTA 開發主管表示，連接馬來西亞、越南、新加坡及泰國的 16 對光纖海底電纜，預估長 2,500 公里、成本約 4 億美元，將在日本 NEC 與法國 Alcatel Submarine Networks 間選擇供應商，目標 2028 年底啟用。工程尚未決標，越南資料中心園區也仍處可行性研究階段。海纜可提供跨國資料中心及雲端流量互連；相關股東含越南 Stavian、日本 Midas Capital 與馬來西亞 OMS Group 子公司 LitUp Network，後者預定負責鋪設工程。海纜容量、陸上機房電力、光纖上線及雲端承租並非相同進度。Reuters 引述開發商稱仍待招標定案；USTDA 於 9 月 23 日公告，資助越南胡志明市 Stavian Digital Park 的供電、散熱與連接設施可行性研究，該研究並不等於園區已取得建廠融資。開發商對供應商排除條件的早期發言之後已澄清為個人看法，不應作為採購禁令。未公布最終海纜供應商、確定合約價格、路線許可、登陸站、測試容量與越南資料中心最終投資額；4 億美元及 2028 年底均為預估。地點：計畫連接越南、馬來西亞、新加坡及泰國；登陸站點未公布。關聯機房園區規劃位於越南胡志明市。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C14" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="294" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">馬國總理披露 500 億美元 AI 與資料中心投資意向，未公告專案核准
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">馬來西亞總理安華 10 月 24 日在馬六甲表示，一名國際投資人於視訊會議中提出約 500 億美元的 AI、新科技與資料中心投資意向，地點包括砂拉越古晉及馬來西亞半島。新加坡《商業時報》10 月 25 日將投資人指為 SoftBank 創辦人孫正義，但尚無 SoftBank 正式投資承諾、核准專案、供電容量或動工日期公告。大型資料中心計畫涉及伺服器與機櫃 ODM、UPS 與電力轉換、冷卻設備、變電系統和光纖互連。安華亦談及半導體人才及向較高附加價值技術環節發展，但並未宣布半導體晶圓廠新案。馬來西亞國家通訊社 Bernama 記錄安華於 10 月 24 日公開發言，投資人意向來自前一週二的視訊會議。新加坡《商業時報》 25 日補充投資人姓名，並指 SoftBank 尚未回應置評要求；兩篇報導均未取得具體合約或許可文件。500 億美元是總理轉述的跨領域投資意向，沒有逐年撥款表、各州配置或已支付金額，不能計入核准 FDI、已建置機房容量或設備採購。投資人正式企業公告、土地權利、電網併接與需量、冷卻用水、專案融資、機房建照及交付時程尚未公布。地點：馬來西亞砂拉越州古晉及馬來西亞半島（擬投資地區，無已核實工地）；發言活動於馬六甲 Hang Jebat 運動場。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C15" s="6">
-        <v>46319</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="162" customHeight="1">
+    <row r="16" ht="214" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -831,25 +831,25 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">新加坡有條件核准跨境進口電力 1.3GW，目標 2035 年開始供應
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">EMA 於 10 月 26 日有條件核准 Sembcorp Utilities 輸入最多 1.3GW 低碳電力，規劃由越南與馬來西亞供應新加坡，目標 2035 年供電。計畫包含越南離岸風電及馬國太陽能與儲能，但仍待多國許可、購電協議及融資。跨國電力走廊涉及輸變電、電源轉換、儲能及資料中心供電。1.3GW 是有條件核准額度，並非實際併網或發電容量。參與企業包括 Petronas、TNB 及越南 PTSC，早於 2025 年 5 月簽訂共同開發協議。10 月 26 日新增條件性核准，後續還須完成跨境許可與融資。實際線路場址、建設經費、購電價格與正式併網時程尚未確定。</t>
+            <t xml:space="preserve">追蹤：中華精測高階探針卡第三季近 4 億元，2027 年第一季產能目標達 2025 年底 3 倍
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">中華精測 10 月 28 日法說指出，今年第三季高階探針卡營收接近 4 億元，約占單季營收 21%，高效能運算（HPC）業務占比 65.9%。公司表示今年 8 月產能已達 2025 年底的 2 倍，並規劃 2027 年第一季達 3 倍；這是前一日財報以外新增的產品與擴產進度。探針卡、晶圓測試板及高功率老化測試板支援 GPU、TPU、ASIC 和矽光子 CPO 的晶圓與封裝測試。高頻訊號、電力完整性和高溫耐受規格因產品而異。公司表示高階 CPU 探針卡工程驗證樣品預計 11 月出貨，量產仍以 2027 年為目標；CPO 測試介面正在與五家以上企業洽談。已核實的是公司當日陳述，不代表所有客戶驗證完成。未披露各產線絕對測試通道、測試介面月產能、已驗收客戶清單及高功率老化板出貨量。</t>
           </r>
         </is>
       </c>
       <c r="C16" s="6">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">電力轉換與機房供電設備業者可核對輸配電規格、電池配置及購電合約。尚無施工與融資定案資料，無法推估供應商設備交付。</t>
+          <t xml:space="preserve">測試電源、探針台和高功率老化設備供應商需確認 HPC 探針卡的功率密度、通道數和客戶驗收時程。倍數產能目標沒有絕對片數，無法據此推算裝機量。</t>
         </is>
       </c>
     </row>
@@ -868,29 +868,29 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">台達電泰國子公司擬取得 3,450 萬美元設備，賣方為集團新加坡公司
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台達電 10 月 27 日代泰國子公司 DET 公告，董事會決議向同集團新加坡子公司 DEIL-SG 取得供營業使用設備，總交易金額約 3,450 萬美元，說明與轉型智慧工廠的製造策略有關。此為關係人間設備資產交易，不等同於新增跨境外商投資或設備已全部驗收。設備轉移可能涉及產線自動化、產能配置與集團廠區間資產管理；公告僅以『供營業使用設備』描述，未提供品項和製造線別。中央社引述上市公司 10 月 27 日重大訊息，交易由 DET 董事會決議，對手方為台達電新加坡子公司，交易金額約美金 3,450 萬。公告列明議價及電匯，不是新加坡外部企業對泰國的新股權投資。設備清單、所在廠址、原值、安裝時程、產能變動與實際付款日期未公布。地點：泰國 DET 子公司（實際設備裝設廠址未公告）；交易相對方位於新加坡。</t>
+            <t xml:space="preserve">金鞍機械桃園龍潭新廠啟用，布局儲冰空調及工業無人載具設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">義美關係企業金鞍機械 10 月 28 日在桃園龍潭啟用投資逾 10 億元的新製造大樓，預計承製逾 20 座大型離峰儲冰空調系統供集團廠區使用。公司稱義美既有龍潭廠導入儲冰空調後，尖峰用電需求下降約 25% 至 30%；此為特定廠區陳述，不代表所有資料中心或工廠能取得相同節電幅度。儲冰空調夜間製冰、白天釋冷，屬工廠空調冷負載移轉，不等同於液冷機櫃冷板、晶片散熱效能或總用電量降低。無人載具及極端環境測試為新廠另一研發方向。公司表示新大樓包含冷凍真空乾燥、儲冰系統及無人載具製造；逾 10 億元是投資額陳述，尚未拆分工程與機台支出。逾 20 座系統為計畫承製數量。未公布建置工期、各套儲冰系統額定 kW、實際耗電度數及對外客戶完成驗收數。地點：台灣桃園市龍潭區，金鞍機械製造新大樓（新廠啟用地點，詳細地址未取得）。</t>
           </r>
         </is>
       </c>
       <c r="C17" s="6">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">智慧工廠電源、控制與測試系統業者可核對移轉設備類別、既有與新增裝機占比以及驗收階段。關係人交易價值不等於泰國廠新增加的生產能力。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="242" customHeight="1">
+          <t xml:space="preserve">工業冷卻、壓縮機驅動及電力控制供應商需確認儲冰容量、負載曲線和峰時需量計算方式。個別廠區降低尖峰負載並不等於所有製造或機房情境可直接複製。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="310" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -905,29 +905,29 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">玉晶光公告 9 月自結淨利 4.34 億元，3M 私募股款已匯入
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光 10 月 23 日公告自結 9 月歸屬母公司淨利約新台幣 4.34 億元，年減 15%，每股盈餘 3.85 元；同日媒體報導 3M 認購私募股款約 48.13 億元已匯入。雙方先前公布合作研發擴束光學（EBO）、共封裝光學與資料中心互連產品，但尚未公布量產客戶驗收或出貨量；股款入帳不等於新產品量產。玉晶光現有精密光學製造能力將支援 3M 的 EBO 光連接套管及光互連模組研製，供應鏈涉及精密材料、光學零組件、先進封裝與資料中心交換連接。自結損益反映既有業務，無法單獨歸因於尚未量產的光學互連合作。3M 10 月 19 日第一手公告稱擬取得玉晶光約 4.7% 股權，原計畫須完成慣例交割條件；10 月 23 日媒體說股款已匯入。玉晶光第三季營收約 78.12 億元、年增約 1%，歸屬母公司淨利約 10.92 億元、年減 23%，依中央社當日報導口徑，季度數字與單月不同。私募法律程序最終交割日、EBO 製造良率、客戶認證和出貨排程尚未完全披露；9 月及第三季損益屬公司自結。</t>
+            <t xml:space="preserve">MViSTA 海纜開發商稱將於 10 月決標，規劃串聯東南亞四國與越南資料中心
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">Reuters 10 月 22 日引述越南 Stavian 旗下 MViSTA 開發主管表示，連接馬來西亞、越南、新加坡及泰國的 16 對光纖海底電纜，預估長 2,500 公里、成本約 4 億美元，將在日本 NEC 與法國 Alcatel Submarine Networks 間選擇供應商，目標 2028 年底啟用。工程尚未決標，越南資料中心園區也仍處可行性研究階段。海纜可提供跨國資料中心及雲端流量互連；相關股東含越南 Stavian、日本 Midas Capital 與馬來西亞 OMS Group 子公司 LitUp Network，後者預定負責鋪設工程。海纜容量、陸上機房電力、光纖上線及雲端承租並非相同進度。Reuters 引述開發商稱仍待招標定案；USTDA 於 9 月 23 日公告，資助越南胡志明市 Stavian Digital Park 的供電、散熱與連接設施可行性研究，該研究並不等於園區已取得建廠融資。開發商對供應商排除條件的早期發言之後已澄清為個人看法，不應作為採購禁令。未公布最終海纜供應商、確定合約價格、路線許可、登陸站、測試容量與越南資料中心最終投資額；4 億美元及 2028 年底均為預估。地點：計畫連接越南、馬來西亞、新加坡及泰國；登陸站點未公布。關聯機房園區規劃位於越南胡志明市。</t>
           </r>
         </is>
       </c>
       <c r="C18" s="6">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="258" customHeight="1">
+          <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="294" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -942,29 +942,29 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">長榮航稱高科技空運需求持續，9 月貨運營收年增 42.55%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">長榮航空總經理孫嘉明 10 月 25 日在台北受訪表示，AI 伺服器及其他高科技貨運需求全年維持強勁，帶動運價，但航空燃油上漲仍是重要成本變數。公司先前公布的 9 月貨運營收為新台幣 61.67 億元、年增 42.55%，此為歷史月份實績，並非 10 月 25 日新增出貨量。航空貨運與台灣出口的 AI 伺服器、伺服器機櫃、半導體設備及高價值電子零組件有直接物流連結。不同貨型對載重、艙位、時效及地面操作要求不同，空運貨值與設備實際產能無法直接相比。長榮航管理階層 10 月 25 日表示航空油價曾達每桶約 177 美元，公司調整部分票價與運價，並指出高科技空運需求持續。9 月合併營收 207.49 億元、貨運營收 61.67 億元為先前公告實績，不能全部歸因於 AI 類貨物。貨運營收年增 42.55% 同時反映貨量、運價與運送組合，現有報導未提供分離量價因素的同期比較表。每桶 177 美元為受訪者引用的先前燃油水準，不是 10 月 25 日官方即時成交價格。未公布當日貨機裝載率、各類 AI 貨物實際噸數、客戶長約、燃油避險覆蓋或跨境專用運力新增合約。</t>
+            <t xml:space="preserve">馬國總理披露 500 億美元 AI 與資料中心投資意向，未公告專案核准
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞總理安華 10 月 24 日在馬六甲表示，一名國際投資人於視訊會議中提出約 500 億美元的 AI、新科技與資料中心投資意向，地點包括砂拉越古晉及馬來西亞半島。新加坡《商業時報》10 月 25 日將投資人指為 SoftBank 創辦人孫正義，但尚無 SoftBank 正式投資承諾、核准專案、供電容量或動工日期公告。大型資料中心計畫涉及伺服器與機櫃 ODM、UPS 與電力轉換、冷卻設備、變電系統和光纖互連。安華亦談及半導體人才及向較高附加價值技術環節發展，但並未宣布半導體晶圓廠新案。馬來西亞國家通訊社 Bernama 記錄安華於 10 月 24 日公開發言，投資人意向來自前一週二的視訊會議。新加坡《商業時報》 25 日補充投資人姓名，並指 SoftBank 尚未回應置評要求；兩篇報導均未取得具體合約或許可文件。500 億美元是總理轉述的跨領域投資意向，沒有逐年撥款表、各州配置或已支付金額，不能計入核准 FDI、已建置機房容量或設備採購。投資人正式企業公告、土地權利、電網併接與需量、冷卻用水、專案融資、機房建照及交付時程尚未公布。地點：馬來西亞砂拉越州古晉及馬來西亞半島（擬投資地區，無已核實工地）；發言活動於馬六甲 Hang Jebat 運動場。</t>
           </r>
         </is>
       </c>
       <c r="C19" s="6">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="214" customHeight="1">
+          <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="162" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -979,16 +979,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">Reuters：ASMPT 的 SMT 業務出售仍在競標，尚無完成交易
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">Reuters 10 月 26 日引述匿名人士稱，IDG Capital 在新加坡總部 ASMPT 的 SMT 事業洽購中較為領先，潛在交易價值可能逾 10 億美元，但尚未定案。ASMPT 於 2026 年 1 月啟動策略檢視，原始公告列出售、合資、分拆、上市或保留等多種選項。SMT 設備涉及電子板件印刷、貼片、檢測及產線軟體，應用於 AI 伺服器、光收發器及汽車電子組裝。競標報導尚不能證明設備支援與保固安排將改變。Reuters 引述上半年業務數據：SMT 營收年增 53.1% 至 38.7 億港元，接單年增 87.8% 至 69.8 億港元。上述為上半年歷史實績，新消息僅是洽購進度。未簽正式出售合約，買方、價金、監管申報及員工安排均未證實。</t>
+            <t xml:space="preserve">新加坡有條件核准跨境進口電力 1.3GW，目標 2035 年開始供應
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">EMA 於 10 月 26 日有條件核准 Sembcorp Utilities 輸入最多 1.3GW 低碳電力，規劃由越南與馬來西亞供應新加坡，目標 2035 年供電。計畫包含越南離岸風電及馬國太陽能與儲能，但仍待多國許可、購電協議及融資。跨國電力走廊涉及輸變電、電源轉換、儲能及資料中心供電。1.3GW 是有條件核准額度，並非實際併網或發電容量。參與企業包括 Petronas、TNB 及越南 PTSC，早於 2025 年 5 月簽訂共同開發協議。10 月 26 日新增條件性核准，後續還須完成跨境許可與融資。實際線路場址、建設經費、購電價格與正式併網時程尚未確定。</t>
           </r>
         </is>
       </c>
@@ -997,7 +997,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMT 電源、測試及設備服務供應商可追蹤正式買方與保固責任是否變更。未有已簽合約，不應推定採購或客戶合約轉移。</t>
+          <t xml:space="preserve">電力轉換與機房供電設備業者可核對輸配電規格、電池配置及購電合約。尚無施工與融資定案資料，無法推估供應商設備交付。</t>
         </is>
       </c>
     </row>
@@ -1016,16 +1016,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">力成先進封裝營收占比逾三成，第三季封測稼動率逾九成
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">力成 10 月 27 日法說公布第三季營收 253.34 億元、毛利率 24%、歸母淨利 26.12 億元；公司稱先進封裝營收占比已逾三成，第三季封裝與測試產能利用率逾九成。FOPLP 客戶驗證仍在進行，2027 年量產及新加坡投資進度均尚未確定完成。公司業務涵蓋 DRAM、NAND／eSSD 與邏輯封測，新規劃包含 FOPLP、FCBGA、2.5D／3D 異質整合及 CPO 光學引擎。這些製程分屬不同封裝產品，不應合併為已量產的同一產能。公司稱第三季大型晶片 FCBGA 已導入量產，第四季規劃更大尺寸；FOPLP 仍為 2027 年量產目標。董事長表示不排除與晶圓廠合作，但尚無正式策略聯盟合約。FOPLP 客戶認證、絕對月產能、新加坡投資金額與實際交付時點未公布。</t>
+            <t xml:space="preserve">台達電泰國子公司擬取得 3,450 萬美元設備，賣方為集團新加坡公司
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台達電 10 月 27 日代泰國子公司 DET 公告，董事會決議向同集團新加坡子公司 DEIL-SG 取得供營業使用設備，總交易金額約 3,450 萬美元，說明與轉型智慧工廠的製造策略有關。此為關係人間設備資產交易，不等同於新增跨境外商投資或設備已全部驗收。設備轉移可能涉及產線自動化、產能配置與集團廠區間資產管理；公告僅以『供營業使用設備』描述，未提供品項和製造線別。中央社引述上市公司 10 月 27 日重大訊息，交易由 DET 董事會決議，對手方為台達電新加坡子公司，交易金額約美金 3,450 萬。公告列明議價及電匯，不是新加坡外部企業對泰國的新股權投資。設備清單、所在廠址、原值、安裝時程、產能變動與實際付款日期未公布。地點：泰國 DET 子公司（實際設備裝設廠址未公告）；交易相對方位於新加坡。</t>
           </r>
         </is>
       </c>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">先進封裝設備、測試電源及量測介面供應商需要確認 FOPLP 與高階 FCBGA 實際通過客戶認證的封裝尺寸、產線設備要求及交付里程碑。第三季稼動率與 2027 年擴產計畫屬不同時點，不能直接換算設備需求。</t>
+          <t xml:space="preserve">智慧工廠電源、控制與測試系統業者可核對移轉設備類別、既有與新增裝機占比以及驗收階段。關係人交易價值不等於泰國廠新增加的生產能力。</t>
         </is>
       </c>
     </row>
@@ -1053,6 +1053,228 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">台達電第三季營收 1,970.59 億元、歸母淨利 234.95 億元，29 日將召開法說
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台達電 10 月 28 日公布第三季營收新台幣 1,970.59 億元、歸母淨利 234.95 億元，每股盈餘 9.04 元；營收年增約 31%，獲利季減 6.5%。公司預定 10 月 29 日法說會說明後續電源及散熱業務展望，尚不能提前寫成正式財測。台達電營運涵蓋伺服器電源、資料中心供電、熱管理、工業自動化及能源設備。合併營收涵蓋多部門，不等於 AI 機櫃電源的獨立出貨收入。第三季毛利率 34.08%，較上年同期減少 0.79 個百分點；歸母淨利年增 26.3% 但季減 6.5%。數值屬正式財報，尚無 29 日法說的後續明確出貨及產品別財測。未公布本次可直接核對的 HVDC／液冷／機櫃電源個別營收與獲利，也沒有 29 日法說的正式展望。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C22" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電源轉換與工業量測供應商應分清集團財報與資料中心電源各產品的實際交付量，並核對後續法說是否揭露新款產品驗收。財報數值不能直接推算新增機櫃設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="210" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">是方第三季營收 10.77 億元，聯雲 LY2 年底進駐率目標八成
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">是方 10 月 28 日公布第三季營收 10.77 億元、毛利率 51.5%、稅後淨利 3.32 億元。公司說聯雲 LY2 資料中心客戶進駐率逐季提高，目標年底達八成；虎尾 AI 資料中心已於 10 月 20 日動土，規劃 2028 年下半年營運，但沒有公布已完成裝機的 IT 負載或新增機櫃數。資料中心需求涉及機房配電、UPS、散熱及跨境網路連接。進駐率是租用或客戶使用比例，不能直接視為機房滿載電力或 GPU 運算使用率。管理層指出今年起 LY2 折舊費用完整認列，第三季毛利率仍高於上半年 48.55% 的水準；年末進駐率八成是目標，尚非 10 月 28 日的實際占用率。未披露最新實際進駐率、總可用機架、已供電 MW、冷卻密度及虎尾機房核定容量。地點：台灣台北市聯雲 LY2 資料中心（已營運機房）；雲林縣虎尾鎮另有規劃中的 AI 機房工地。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C23" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機房電源、UPS 和液冷業者需確認進駐率定義、實際獲供電的機架和每機櫃功率。進駐率八成為管理層預期，尚不能換算已採購設備數量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="242" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光公告 9 月自結淨利 4.34 億元，3M 私募股款已匯入
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">玉晶光 10 月 23 日公告自結 9 月歸屬母公司淨利約新台幣 4.34 億元，年減 15%，每股盈餘 3.85 元；同日媒體報導 3M 認購私募股款約 48.13 億元已匯入。雙方先前公布合作研發擴束光學（EBO）、共封裝光學與資料中心互連產品，但尚未公布量產客戶驗收或出貨量；股款入帳不等於新產品量產。玉晶光現有精密光學製造能力將支援 3M 的 EBO 光連接套管及光互連模組研製，供應鏈涉及精密材料、光學零組件、先進封裝與資料中心交換連接。自結損益反映既有業務，無法單獨歸因於尚未量產的光學互連合作。3M 10 月 19 日第一手公告稱擬取得玉晶光約 4.7% 股權，原計畫須完成慣例交割條件；10 月 23 日媒體說股款已匯入。玉晶光第三季營收約 78.12 億元、年增約 1%，歸屬母公司淨利約 10.92 億元、年減 23%，依中央社當日報導口徑，季度數字與單月不同。私募法律程序最終交割日、EBO 製造良率、客戶認證和出貨排程尚未完全披露；9 月及第三季損益屬公司自結。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C24" s="6">
+        <v>46318</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="258" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">長榮航稱高科技空運需求持續，9 月貨運營收年增 42.55%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">長榮航空總經理孫嘉明 10 月 25 日在台北受訪表示，AI 伺服器及其他高科技貨運需求全年維持強勁，帶動運價，但航空燃油上漲仍是重要成本變數。公司先前公布的 9 月貨運營收為新台幣 61.67 億元、年增 42.55%，此為歷史月份實績，並非 10 月 25 日新增出貨量。航空貨運與台灣出口的 AI 伺服器、伺服器機櫃、半導體設備及高價值電子零組件有直接物流連結。不同貨型對載重、艙位、時效及地面操作要求不同，空運貨值與設備實際產能無法直接相比。長榮航管理階層 10 月 25 日表示航空油價曾達每桶約 177 美元，公司調整部分票價與運價，並指出高科技空運需求持續。9 月合併營收 207.49 億元、貨運營收 61.67 億元為先前公告實績，不能全部歸因於 AI 類貨物。貨運營收年增 42.55% 同時反映貨量、運價與運送組合，現有報導未提供分離量價因素的同期比較表。每桶 177 美元為受訪者引用的先前燃油水準，不是 10 月 25 日官方即時成交價格。未公布當日貨機裝載率、各類 AI 貨物實際噸數、客戶長約、燃油避險覆蓋或跨境專用運力新增合約。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="214" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">Reuters：ASMPT 的 SMT 業務出售仍在競標，尚無完成交易
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">Reuters 10 月 26 日引述匿名人士稱，IDG Capital 在新加坡總部 ASMPT 的 SMT 事業洽購中較為領先，潛在交易價值可能逾 10 億美元，但尚未定案。ASMPT 於 2026 年 1 月啟動策略檢視，原始公告列出售、合資、分拆、上市或保留等多種選項。SMT 設備涉及電子板件印刷、貼片、檢測及產線軟體，應用於 AI 伺服器、光收發器及汽車電子組裝。競標報導尚不能證明設備支援與保固安排將改變。Reuters 引述上半年業務數據：SMT 營收年增 53.1% 至 38.7 億港元，接單年增 87.8% 至 69.8 億港元。上述為上半年歷史實績，新消息僅是洽購進度。未簽正式出售合約，買方、價金、監管申報及員工安排均未證實。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C26" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMT 電源、測試及設備服務供應商可追蹤正式買方與保固責任是否變更。未有已簽合約，不應推定採購或客戶合約轉移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="194" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">力成先進封裝營收占比逾三成，第三季封測稼動率逾九成
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">力成 10 月 27 日法說公布第三季營收 253.34 億元、毛利率 24%、歸母淨利 26.12 億元；公司稱先進封裝營收占比已逾三成，第三季封裝與測試產能利用率逾九成。FOPLP 客戶驗證仍在進行，2027 年量產及新加坡投資進度均尚未確定完成。公司業務涵蓋 DRAM、NAND／eSSD 與邏輯封測，新規劃包含 FOPLP、FCBGA、2.5D／3D 異質整合及 CPO 光學引擎。這些製程分屬不同封裝產品，不應合併為已量產的同一產能。公司稱第三季大型晶片 FCBGA 已導入量產，第四季規劃更大尺寸；FOPLP 仍為 2027 年量產目標。董事長表示不排除與晶圓廠合作，但尚無正式策略聯盟合約。FOPLP 客戶認證、絕對月產能、新加坡投資金額與實際交付時點未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先進封裝設備、測試電源及量測介面供應商需要確認 FOPLP 與高階 FCBGA 實際通過客戶認證的封裝尺寸、產線設備要求及交付里程碑。第三季稼動率與 2027 年擴產計畫屬不同時點，不能直接換算設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="198" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">中華精測第三季營收 19.05 億元、淨利 5.51 億元，晶圓測試卡占前九月營收 71%
 </t>
           </r>
@@ -1066,22 +1288,59 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="6">
+      <c r="C28" s="6">
         <v>46322</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">高頻測試電源與探針卡設備業者可核對實際驗證通道、訊號與電源完整性標準，以及下一代測試卡的客戶接受節點。營收結構不能直接換算設備採購或實際測試吞吐量。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="262" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="29" ht="178" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">穩懋第三季營收 58.59 億元，光接收元件尚在產能爬坡
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">穩懋 10 月 28 日公布第三季營收 58.59 億元、毛利率 37.4%，歸母淨利 19.3 億元；公司稱光通訊接收端 PD 元件仍處初期量產爬坡，較大規模出貨目標落在 2028 年。衛星通訊及點對點通訊需求與公司基礎設施業務相關，但並未公布各應用的獨立出貨件數。穩懋的砷化鎵 RF 和光接收元件連結衛星、光通訊及資料中心光模組等用途。產品銷售成長和前段晶圓製程擴產是不同概念。公司表示毛利率較第二季提高 9.2 個百分點，獲利季增約 98%。預估第四季營收僅低個位數增長，手機業務因記憶體價格影響仍面臨需求變化。未披露 PD 產品絕對月出貨量、合格良率、主要客戶及 2028 年產能配置。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">射頻製程電源與光學量測供應商需確認 PD 製程良率、接收端產品類型與測試頻寬。較大出貨為遠期規劃，不能從本期集團獲利推算光模組產量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="262" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1103,22 +1362,22 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="6">
+      <c r="C30" s="6">
         <v>46319</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="246" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="31" ht="246" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1140,22 +1399,22 @@
           </r>
         </is>
       </c>
-      <c r="C24" s="6">
+      <c r="C31" s="6">
         <v>46321</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">晶圓製程電源、量測與廠務設備業者可追問正式機台採購、技術合約與開工許可。現地觀察和業者回覆存在差異，不能把 2027 年當作已確認的量產日期。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="198" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="32" ht="198" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1177,12 +1436,86 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="6">
+      <c r="C32" s="6">
         <v>46322</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">晶圓製程電源與先進封裝測試業者會確認實際代工場、封裝介面、矽智財驗證及後續晶片試產時程。專案 NRE 金額並非晶圓代工或設備採購支出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="226" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">聯電董事會追加約 32 億美元擴產預算，指向新加坡與南科
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">聯電 10 月 28 日董事會通過約 32 億美元追加擴產預算，公司表示將用於加快新加坡與南科擴建進度，但未提供新產能逐月開出日期。第三季合併營收 742.4 億元、毛利率 34%，12 吋約當晶圓出貨逾 120 萬片，產能利用率達 92%。晶圓代工產能包括成熟節點與 22／28 奈米特殊製程，涉及電源管理 IC、連接晶片、矽光子和工業控制。追加核准資金不等於設備已裝機或支出已發生。聯電原定 2026 年資本支出約 20 億美元，此次為董事會另外核准的擴產預算，不應與季度費用混為一談。公司預估第四季出貨季增 1% 至 3%、稼動率約 91% 至 93%，2027 年平均售價年增 10% 為管理階層預期，非已簽實績。沒有分廠核定支出配置、採購設備清單、投片擴增量、實際動工或轉量產日期；遠期平均售價及 AI 營收占比均為預測。地點：台灣台南科學園區及新加坡既有與規劃廠區（擴產所在區域，未指定新增廠房地址）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C33" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源、量測和先進封裝設備供應商需核對新加坡與南科分別核准的工具規格、採購及設備驗收時點。現階段只有董事會授權額與現有稼動率，尚不足以量化未來交付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="214" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞海關公布查扣 30 台伺服器，疑載價值約 4,950 萬令吉 AI 晶片
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞海關 10 月 28 日公布，本月 15 日在吉隆坡國際機場自由貿易區查獲 30 台伺服器，內含疑涉違規轉運的高階 AI 晶片，估值約 4,950 萬令吉。貨物據稱以電子零組件申報，原產國、目的地、晶片型號和最終責任仍在調查，不能視為已確認走私判決。跨境伺服器、GPU 與晶片組件的出口管制及轉運許可對資料中心供應鏈有直接影響。海關查獲貨件與合法跨境伺服器出貨須分開，案件數量不能代表市場正常運量。Reuters 引述海關表示貨運需申請貿易許可，且已調查至少五宗可能相關案件，累計查扣晶片價值逾 1 億令吉；其中 4,950 萬令吉為本次 10 月 15 日查獲批次。尚無起訴及判決、原始和目的國、晶片性能及客戶名稱，也未確認貨物最終處理方式。地點：馬來西亞雪蘭莪州雪邦，吉隆坡國際機場自由貿易區（海關查獲地）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C34" s="6">
+        <v>46310</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器與測試設備物流相關業者須區分轉運申報、原產地文件與出口許可要求。案件仍在調查，不能推論任何已具名供應商涉及違法行為。</t>
         </is>
       </c>
     </row>

--- a/docs/exports/week-2026-10-25.xlsx
+++ b/docs/exports/week-2026-10-25.xlsx
@@ -134,22 +134,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">記憶體模組、材料與高速晶片供應
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">工研院提出稀土材料規劃、騰輝泰國銅箔基板廠已小量出貨，旺宏記憶體擴產仍待 2027 年開出。十銓 10 月 28 日提出新北模組廠 2027 年第二季投產目標；譜瑞則預估第四季高速介面晶片營收季減，這些數字分屬實際、規劃及財測。</t>
+            <t xml:space="preserve">記憶體、被動元件與電子材料供應
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">工研院與泰國騰輝新廠反映稀土及 PCB 材料規劃，旺宏新增 NAND／eMMC 產能、十銓新北模組廠仍待 2027 年開出。國巨 10 月 29 日公布第三季 AI 應用近兩成、MLCC 與鉭電容稼動率接近 95%，未來擴產尚待驗收。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/24、10/26、10/27、10/28</t>
+          <t xml:space="preserve">10/24、10/26、10/27、10/28、10/29</t>
         </is>
       </c>
     </row>
@@ -168,22 +168,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">晶圓測試、工廠自動化與精密設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">颱風後電網復原與鴻海 AI 工廠效率資料各屬不同營運場景；國研院與汎銓發表 High-NA EUV 樣品分析方法。中華精測 10 月 28 日新增探針卡營收與 2027 年產能目標，金鞍機械龍潭廠正式啟用，兩案仍有待確認絕對產能與交付。</t>
+            <t xml:space="preserve">工廠自動化、製程量測與工業設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">本週台電復電、鴻海 AI 工廠效率量測與國研院 High-NA EUV 分析技術各為不同實績。中華精測公布探針卡擴產時程，金鞍機械啟用龍潭冷卻設備廠；研華 10 月 29 日公告第三季營收 324.4 億元及接單出貨比 1.64，數據涵蓋工業電腦與半導體設備需求。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/25、10/26、10/27、10/28</t>
+          <t xml:space="preserve">10/22、10/24、10/25、10/26、10/27、10/28、10/29</t>
         </is>
       </c>
     </row>
@@ -202,22 +202,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">台灣與東南亞資料中心電力及供應鏈
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 海纜仍在招標，馬來西亞 500 億美元資料中心投資意向未具正式專案核准；新加坡跨國電力輸入取得條件性核准。台達電公布第三季合併財報，是方電訊報告機房業績與 LY2 進駐率目標；各案的財務實績、投資意向及已併網容量不可混為一談。</t>
+            <t xml:space="preserve">資料中心供電、伺服器資金及東南亞能源零組件
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">MViSTA 海纜招標、馬來西亞資料中心投資意向及新加坡 1.3GW 條件性輸電核准仍未等於機房完工。台達電 29 日說明機房延遲與存貨跌價，技嘉核准 500 億元聯貸，泰國經寶精密則描述 BBU 與電源櫃機構件量產爬坡；三者屬營運說明、融資授權及產線目標。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/26、10/27、10/28</t>
+          <t xml:space="preserve">10/22、10/24、10/26、10/27、10/28、10/29</t>
         </is>
       </c>
     </row>
@@ -236,26 +236,26 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">先進封裝、光通訊與電子測試設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">玉晶光與 3M 光互連合作尚未公布量產客戶驗收；力成先進封裝營收占比已逾三成，FOPLP 仍待量產認證。ASMPT SMT 交易仍屬未簽約洽談，穩懋 10 月 28 日公布光接收 PD 產能爬坡與第三季財報，不能將遠期出貨目標視為已交付。</t>
+            <t xml:space="preserve">先進封裝、光通訊與半導體測試設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">力成先進封裝營收占比與精測探針卡財報為本週已公布數字，FOPLP 與 CPO 仍有產品認證階段；ASMPT SMT 出售未簽約，穩懋光接收產品在產能爬坡。京元電 10 月 29 日公布德州新測試廠土地建物及約 5.34 億美元設備取得，2027 年量產仍屬目標。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/23、10/25、10/26、10/27、10/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="114" customHeight="1">
+          <t xml:space="preserve">10/23、10/25、10/26、10/27、10/28、10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="98" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
@@ -270,22 +270,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">晶圓製造、跨境合作及晶片監管
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台菲半導體經濟走廊仍為政策討論，Reuters 先前報導越南 Viettel 晶圓廠工地與 DUV 採購未完成，智原另宣布 2 奈米晶片委託設計案。聯電 10 月 28 日核准追加約 32 億美元擴產預算，馬來西亞海關同日公布 15 日查獲的 AI 晶片伺服器案件；核准資本支出與海關查扣均須保留其性質與日期。</t>
+            <t xml:space="preserve">晶圓廠房、晶片設計及產業政策
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台菲合作仍屬政策議題、越南 Viettel 晶圓廠建造與 DUV 採購尚有爭議，智原取得 2 奈米晶片設計專案，聯電核准追加擴產預算。友達 29 日決議以 388 億元出售台中廠予台積電，TSIA 同日預估全年產值逾 9.1 兆元；資產交易、研發設計、產能授權與總產值預測是不同類型資訊。</t>
           </r>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/15、10/24、10/26、10/27、10/28</t>
+          <t xml:space="preserve">10/15、10/24、10/26、10/27、10/28、10/29</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="246" customHeight="1">
+    <row r="9" ht="214" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">07</t>
@@ -572,6 +572,43 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">國巨第三季營收 495.32 億元，AI 占比近兩成；第四季稼動率逾 95% 為預估
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">國巨 10 月 29 日法說公布第三季合併營收 495.32 億元、毛利率 41%、歸母淨利 119.81 億元；AI 應用營收占比由第二季 16% 上升至接近兩成。公司預估第四季稼動率超過 95%，2027 年分階段擴充約 10% 至 15% 產能，尚未公布新增產能的絕對件數。積層陶瓷電容、鉭質電容及特殊被動元件用於伺服器供電、通訊設備及工業終端。AI 應用占營收比率是公司營收結構，不能直接換算成伺服器機櫃出貨或各類電容產量。國巨表示第三季接單出貨比接近 2，特殊品及標準品稼動率接近 95%，並已與部分大客戶協商長期供貨。第四季及 2027 年數值是公司預期，與第三季已認列營收不同。未披露 AI 相關 MLCC 及鉭電容的獨立產量、2027 年擴產絕對片數、客戶合約價與新設備支出金額。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器電源轉換和電子量測供應商需確認被動元件的功率、溫度與可靠度規格，以及擴產項目的實際產線驗收時程。營收占比及管理階層稼動率預估不足以量化未來設備採購。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="246" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">薔琵颱風造成全台逾 34 萬戶曾停電，台電 10 月 24 日下午稱復電率逾 9 成
 </t>
           </r>
@@ -585,22 +622,22 @@
           </r>
         </is>
       </c>
-      <c r="C9" s="6">
+      <c r="C10" s="6">
         <v>46319</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對供電設備與工業電力品質業者，應區分配電故障與廠區內備援系統失效，確認鹽塵環境下的絕緣設計、UPS 或儲能切換與實際停電波形。缺少個別工廠測量記錄，無法推定設備停機或產能損失。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="178" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+    <row r="11" ht="178" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -622,22 +659,22 @@
           </r>
         </is>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="6">
         <v>46317</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工業控制電源、工業視覺測試與邊緣運算硬體供應商可確認新公司實際採用的攝影機、伺服器及邊緣裝置規格與驗收條件。尚無部署數量及工廠應用簽約資訊。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="242" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="242" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -659,49 +696,12 @@
           </r>
         </is>
       </c>
-      <c r="C11" s="6">
+      <c r="C12" s="6">
         <v>46320</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程電源、UPS 和廠務監控供應商可查明各廠是否有實際電壓驟降、儲能切換或異常警報。家庭戶數復電不揭露機台開機狀態，因此不能換算設備停產或備援採購。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="146" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">鴻海與 NVIDIA 公布智慧工廠實測：排程工時減 25%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">鴻海與 NVIDIA 10 月 26 日公布特定智慧工廠流程數據，生產排程工時降低 25%，射出工程工作量降低 50%。DGX 平台的特定模型訓練速度為既有 H100 系統的 2.48 倍，尚未提供跨廠驗證。製造應用涵蓋 SMT、排程、自動化、工業量測與伺服器 AI 訓練平台。NVIDIA 指出測試以既有 H100 平台為比較基準，且 12 天處理 1 兆 Token；流程改善數據不可視為整體工廠平均成效。受測廠區、絕對工時及產線良率比較資料未公布。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C12" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製程量測與工業電源供應商可核對導入範圍及基準工時。缺乏跨廠數據，尚無法推定全面效益。</t>
         </is>
       </c>
     </row>
@@ -720,16 +720,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">JIMTOF 東京開展，公會表示有 94 家台灣廠商參展
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">日本工具機展 JIMTOF 於 10 月 26 日在東京國際展示場開展，展期至 31 日。台灣工具機公會稱有 94 家台廠參展，包含 CNC、量測與工廠自動化設備；實際成交額及設備訂單未公布。精密加工及控制設備涉及工廠自動化與半導體設備零組件製造，展出不等於簽單。主辦方確認 10 月 26 至 31 日於 Tokyo Big Sight 舉行；公會參展家數由中央社轉述。展後成交、客戶驗證及設備採購量尚未公布。地點：日本東京 Tokyo Big Sight（實際展覽場館）。</t>
+            <t xml:space="preserve">鴻海與 NVIDIA 公布智慧工廠實測：排程工時減 25%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">鴻海與 NVIDIA 10 月 26 日公布特定智慧工廠流程數據，生產排程工時降低 25%，射出工程工作量降低 50%。DGX 平台的特定模型訓練速度為既有 H100 系統的 2.48 倍，尚未提供跨廠驗證。製造應用涵蓋 SMT、排程、自動化、工業量測與伺服器 AI 訓練平台。NVIDIA 指出測試以既有 H100 平台為比較基準，且 12 天處理 1 兆 Token；流程改善數據不可視為整體工廠平均成效。受測廠區、絕對工時及產線良率比較資料未公布。</t>
           </r>
         </is>
       </c>
@@ -738,44 +738,44 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">製程量測與工業電源供應商可核對導入範圍及基準工時。缺乏跨廠數據，尚無法推定全面效益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="146" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">JIMTOF 東京開展，公會表示有 94 家台灣廠商參展
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">日本工具機展 JIMTOF 於 10 月 26 日在東京國際展示場開展，展期至 31 日。台灣工具機公會稱有 94 家台廠參展，包含 CNC、量測與工廠自動化設備；實際成交額及設備訂單未公布。精密加工及控制設備涉及工廠自動化與半導體設備零組件製造，展出不等於簽單。主辦方確認 10 月 26 至 31 日於 Tokyo Big Sight 舉行；公會參展家數由中央社轉述。展後成交、客戶驗證及設備採購量尚未公布。地點：日本東京 Tokyo Big Sight（實際展覽場館）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">設備電源與精密量測業者可核實展出技術規格與客戶驗收情況。參展家數不代表新設備訂單。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="178" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">國研院與汎銓公布 High-NA EUV 光阻奈米結構鍍膜檢測技術
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">國研院 10 月 27 日宣布，國儀中心與汎銓合作，在 High-NA EUV 與金屬氧化物光阻（MOR）曝光後，以鍍膜強化奈米結構，支援後續晶圓剖面分析。國研院稱技術已協助汎銓進入大型半導體設備與製造商供應鏈，但未公布已完成驗收的客戶、良率或量產導入規模。在高數值孔徑 EUV 微影後，金屬氧化物光阻形成的微細結構在斷面檢測前須保持形狀。樣品製備與量測結果涉及先進晶圓製程、材料分析及電子顯微技術。國研院指出，以專用鍍膜輔助強化脆弱奈米結構後，可提供後續檢測分析；公開的是研究技術突破，並未表示某製程節點已進入高良率量產。未披露可比較的缺陷率、解析度實驗結果、半導體廠認證時程及商用檢測設備採購量。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C14" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製程量測、電源及分析設備業者可檢查不同光阻與膜層的適用範圍、樣品重現性及實際客戶驗證程序。研究成功不代表已取得量產設備合約。</t>
         </is>
       </c>
     </row>
@@ -794,16 +794,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">宏偉電機稱高載重及無塵室工業電梯訂單能見度達三年
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">宏偉電機 10 月 27 日媒體交流會指出，高載重、無塵室與自動搬運用途電梯的在手訂單能見度延長至三年，今年在手訂單數量較 2025 年增加一倍。公司說半導體周邊相關出貨占比約 59%，客戶涵蓋晶圓、封測與高科技工廠，但未公布可供核對的訂單絕對金額或特定廠房。高載重、無塵室與防爆電梯可用於晶圓、封測和精密工廠的物流與廠務動線。這類建廠周邊設備不等同於曝光、蝕刻或封測機台本身。公司說今年接單出貨比持續逾一，業務涵蓋晶圓代工、半導體設備及後段封測客戶；在手訂單三年是企業口徑，並非確定三年營收額。沒有完整訂單台數、金額、交貨表、最終工地與客戶名稱，亦無可獨立驗證的在手訂單明細。</t>
+            <t xml:space="preserve">國研院與汎銓公布 High-NA EUV 光阻奈米結構鍍膜檢測技術
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">國研院 10 月 27 日宣布，國儀中心與汎銓合作，在 High-NA EUV 與金屬氧化物光阻（MOR）曝光後，以鍍膜強化奈米結構，支援後續晶圓剖面分析。國研院稱技術已協助汎銓進入大型半導體設備與製造商供應鏈，但未公布已完成驗收的客戶、良率或量產導入規模。在高數值孔徑 EUV 微影後，金屬氧化物光阻形成的微細結構在斷面檢測前須保持形狀。樣品製備與量測結果涉及先進晶圓製程、材料分析及電子顯微技術。國研院指出，以專用鍍膜輔助強化脆弱奈米結構後，可提供後續檢測分析；公開的是研究技術突破，並未表示某製程節點已進入高良率量產。未披露可比較的缺陷率、解析度實驗結果、半導體廠認證時程及商用檢測設備採購量。</t>
           </r>
         </is>
       </c>
@@ -812,17 +812,54 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">製程量測、電源及分析設備業者可檢查不同光阻與膜層的適用範圍、樣品重現性及實際客戶驗證程序。研究成功不代表已取得量產設備合約。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="178" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">宏偉電機稱高載重及無塵室工業電梯訂單能見度達三年
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">宏偉電機 10 月 27 日媒體交流會指出，高載重、無塵室與自動搬運用途電梯的在手訂單能見度延長至三年，今年在手訂單數量較 2025 年增加一倍。公司說半導體周邊相關出貨占比約 59%，客戶涵蓋晶圓、封測與高科技工廠，但未公布可供核對的訂單絕對金額或特定廠房。高載重、無塵室與防爆電梯可用於晶圓、封測和精密工廠的物流與廠務動線。這類建廠周邊設備不等同於曝光、蝕刻或封測機台本身。公司說今年接單出貨比持續逾一，業務涵蓋晶圓代工、半導體設備及後段封測客戶；在手訂單三年是企業口徑，並非確定三年營收額。沒有完整訂單台數、金額、交貨表、最終工地與客戶名稱，亦無可獨立驗證的在手訂單明細。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C16" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">工廠電力與自動搬運設備業者可核對實際交付工地、升降設備負載規格及施工驗收。訂單能見度不是已實現營收，也不能用來推估任何晶圓廠的投產日期。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="214" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17" ht="214" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -841,43 +878,6 @@
               <color rgb="FF3B4A44"/>
             </rPr>
             <t xml:space="preserve">中華精測 10 月 28 日法說指出，今年第三季高階探針卡營收接近 4 億元，約占單季營收 21%，高效能運算（HPC）業務占比 65.9%。公司表示今年 8 月產能已達 2025 年底的 2 倍，並規劃 2027 年第一季達 3 倍；這是前一日財報以外新增的產品與擴產進度。探針卡、晶圓測試板及高功率老化測試板支援 GPU、TPU、ASIC 和矽光子 CPO 的晶圓與封裝測試。高頻訊號、電力完整性和高溫耐受規格因產品而異。公司表示高階 CPU 探針卡工程驗證樣品預計 11 月出貨，量產仍以 2027 年為目標；CPO 測試介面正在與五家以上企業洽談。已核實的是公司當日陳述，不代表所有客戶驗證完成。未披露各產線絕對測試通道、測試介面月產能、已驗收客戶清單及高功率老化板出貨量。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C16" s="6">
-        <v>46323</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">測試電源、探針台和高功率老化設備供應商需確認 HPC 探針卡的功率密度、通道數和客戶驗收時程。倍數產能目標沒有絕對片數，無法據此推算裝機量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="194" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">金鞍機械桃園龍潭新廠啟用，布局儲冰空調及工業無人載具設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">義美關係企業金鞍機械 10 月 28 日在桃園龍潭啟用投資逾 10 億元的新製造大樓，預計承製逾 20 座大型離峰儲冰空調系統供集團廠區使用。公司稱義美既有龍潭廠導入儲冰空調後，尖峰用電需求下降約 25% 至 30%；此為特定廠區陳述，不代表所有資料中心或工廠能取得相同節電幅度。儲冰空調夜間製冰、白天釋冷，屬工廠空調冷負載移轉，不等同於液冷機櫃冷板、晶片散熱效能或總用電量降低。無人載具及極端環境測試為新廠另一研發方向。公司表示新大樓包含冷凍真空乾燥、儲冰系統及無人載具製造；逾 10 億元是投資額陳述，尚未拆分工程與機台支出。逾 20 座系統為計畫承製數量。未公布建置工期、各套儲冰系統額定 kW、實際耗電度數及對外客戶完成驗收數。地點：台灣桃園市龍潭區，金鞍機械製造新大樓（新廠啟用地點，詳細地址未取得）。</t>
           </r>
         </is>
       </c>
@@ -886,17 +886,91 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">測試電源、探針台和高功率老化設備供應商需確認 HPC 探針卡的功率密度、通道數和客戶驗收時程。倍數產能目標沒有絕對片數，無法據此推算裝機量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="194" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">金鞍機械桃園龍潭新廠啟用，布局儲冰空調及工業無人載具設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">義美關係企業金鞍機械 10 月 28 日在桃園龍潭啟用投資逾 10 億元的新製造大樓，預計承製逾 20 座大型離峰儲冰空調系統供集團廠區使用。公司稱義美既有龍潭廠導入儲冰空調後，尖峰用電需求下降約 25% 至 30%；此為特定廠區陳述，不代表所有資料中心或工廠能取得相同節電幅度。儲冰空調夜間製冰、白天釋冷，屬工廠空調冷負載移轉，不等同於液冷機櫃冷板、晶片散熱效能或總用電量降低。無人載具及極端環境測試為新廠另一研發方向。公司表示新大樓包含冷凍真空乾燥、儲冰系統及無人載具製造；逾 10 億元是投資額陳述，尚未拆分工程與機台支出。逾 20 座系統為計畫承製數量。未公布建置工期、各套儲冰系統額定 kW、實際耗電度數及對外客戶完成驗收數。地點：台灣桃園市龍潭區，金鞍機械製造新大樓（新廠啟用地點，詳細地址未取得）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C18" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">工業冷卻、壓縮機驅動及電力控制供應商需確認儲冰容量、負載曲線和峰時需量計算方式。個別廠區降低尖峰負載並不等於所有製造或機房情境可直接複製。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="310" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19" ht="214" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">研華第三季營收 324.4 億元、淨利 62.18 億元，半導體設備及邊緣運算需求持續
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">研華 10 月 29 日公布第三季營收 324.4 億元、年增 83%，歸母淨利 62.18 億元、年增 125%，EPS 7.15 元。公司說明半導體設備、邊緣 AI 和智慧醫療的應用需求帶動接單，第三季接單出貨比為 1.64；該比率並不等於收入成長率。工業電腦及嵌入式邊緣系統供工廠自動化、半導體設備與智慧醫療使用。不同區域接單與出貨比率的分母為出貨金額，不是設備產能利用率。研華官方報告第三季營收季增 24%、營業利益 67.95 億元、稅後淨利 62.18 億元。中央社另引述公司說明北美接單出貨比 2.12，歐洲 1.52、中國 1.50；不同地區指標應分開解讀。AI、半導體設備、醫療各項產品的單獨營收與測試裝機數、不同客戶的實際交貨日期尚未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C19" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工業量測、精密電源與半導體設備供應商需對照研華的不同應用產品、區域接單結構與實際交貨。接單出貨比提供需求指標，仍需出貨明細才可確認最終設備使用情境。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="310" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -918,22 +992,22 @@
           </r>
         </is>
       </c>
-      <c r="C18" s="6">
+      <c r="C20" s="6">
         <v>46317</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="294" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="21" ht="294" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -955,22 +1029,22 @@
           </r>
         </is>
       </c>
-      <c r="C19" s="6">
+      <c r="C21" s="6">
         <v>46319</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="162" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="22" ht="162" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -992,22 +1066,22 @@
           </r>
         </is>
       </c>
-      <c r="C20" s="6">
+      <c r="C22" s="6">
         <v>46321</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">電力轉換與機房供電設備業者可核對輸配電規格、電池配置及購電合約。尚無施工與融資定案資料，無法推估供應商設備交付。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="194" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="23" ht="194" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1029,22 +1103,22 @@
           </r>
         </is>
       </c>
-      <c r="C21" s="6">
+      <c r="C23" s="6">
         <v>46322</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">智慧工廠電源、控制與測試系統業者可核對移轉設備類別、既有與新增裝機占比以及驗收階段。關係人交易價值不等於泰國廠新增加的生產能力。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="198" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+    <row r="24" ht="198" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1066,22 +1140,22 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="6">
+      <c r="C24" s="6">
         <v>46323</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">電源轉換與工業量測供應商應分清集團財報與資料中心電源各產品的實際交付量，並核對後續法說是否揭露新款產品驗收。財報數值不能直接推算新增機櫃設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="210" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="25" ht="210" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1103,22 +1177,133 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="6">
+      <c r="C25" s="6">
         <v>46323</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">機房電源、UPS 和液冷業者需確認進駐率定義、實際獲供電的機架和每機櫃功率。進駐率八成為管理層預期，尚不能換算已採購設備數量。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="242" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="26" ht="198" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">追蹤：台達電說明資料中心建置延遲及缺料，第三季存貨跌價約占營收 1.7%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台達電董事長鄭平 10 月 29 日法說表示，第三季部分資料中心建置延遲、供應鏈長短料等因素導致存貨跌價損失，金額約占總營收 1.7%。公司預期第四季營收高於第三季，但供電設備、人力、材料和地方審批等問題仍會影響大型資料中心交付速度。資料中心電源、HVDC、UPS、變電及散熱系統依機房土建與電網可用時間交付，設備製造商的已備料庫存不代表最終客戶已完成機櫃部署。第三季歸母淨利 234.95 億元是 10 月 28 日已公布的歷史實績；29 日新增的是管理階層對存貨跌價、材料匹配及機房建置障礙的解釋。存貨跌價占營收 1.7% 亦不可視為 1.7% 的設備故障率。尚未提供逐機房延遲天數、受影響客戶、第四季實際存貨迴轉額或各電源產品的獨立訂單量。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C26" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">資料中心供電、電源轉換和量測產品供應商需核對客戶電網就緒、工程人力及設備交付驗收節點。存貨損失反映部分時程與供應配置問題，不能直接等同設備品質不良。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="178" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">技嘉董事會通過 500 億元聯貸，資金供償債及 AI 產品營運週轉
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">技嘉 10 月 29 日董事會通過與台灣銀行、兆豐、華南及國泰世華等主辦銀行團簽訂新台幣 500 億元聯合授信合約，資金用途包含償還金融機構借款及中期週轉。公司指出 2027 年 AI 產品備料與採購需求，但授信額度並非已動用資金、已簽客戶訂單或新增營收。技嘉製造主機板、GPU 系統及 AI 伺服器與機櫃設備，營運週轉金可涉及晶片、記憶體及整機備料。銀行聯貸核准本身不代表特定伺服器型號或零組件已投入生產。董事會核准聯合授信條件，銀行包括台灣銀行、兆豐國際、華南及國泰世華。公司未在公告中細分 AI 採購與債務償還分配比例，也沒有揭露實際提款金額。貸款動用率、實際 AI 伺服器物料採購金額、客戶與交機數量、借款成本及具體備貨月份未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器電源、機櫃配電及電子測試設備供應商應核對實際採購排程與客戶驗收條件。聯貸額度無法直接換算為機櫃數、電源模組訂單或晶片出貨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="210" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">泰國經寶精密切入電源櫃及 BBU 機構件，第四季大規模量產為公司目標
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣上市、在泰國生產的經寶精密 10 月 29 日表示，已進入當地電源管理企業的供應鏈，電源櫃、備援電池模組（BBU）及伺服器機構件預計在第四季進入大規模量產。公司另表示完成 20 項 Airbus A350 航太製程認證，但沒有公布電源產品實際出貨量或量產驗收。精密鈑金外殼與電源櫃機構件用於機櫃電力配線、BBU 儲能及伺服器整機，與實際電源轉換模組及電芯製造不同。公司亦供應航太機構件，但航太認證與 AI 電源生產線不可混為同一產品驗證。公司接受記者詢問稱與泰國電源管理業者合作，第四季能源產品轉入大規模生產階段，尚未公開產品名稱、產線或個別客戶的出貨合約。A350 航太製程認證總計 20 項，不能換算成電力模組量產數。未公布電源櫃和 BBU 的月出貨量、電氣測試規格、客戶正式驗收，以及北美機房客戶交付時程。地點：泰國經寶精密製造基地（公司所述營運據點；本次未公布具體廠址）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C28" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機櫃供電、BBU 及工業電源供應商需核對機構件的散熱、絕緣、EMI 和可靠度驗收。公司提及量產規劃，但未揭露交付基數，不應換算成資料中心電源實際部署。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="242" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1140,22 +1325,22 @@
           </r>
         </is>
       </c>
-      <c r="C24" s="6">
+      <c r="C29" s="6">
         <v>46318</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="258" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="30" ht="258" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1177,22 +1362,22 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="6">
+      <c r="C30" s="6">
         <v>46320</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="214" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+    <row r="31" ht="214" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1211,191 +1396,6 @@
               <color rgb="FF3B4A44"/>
             </rPr>
             <t xml:space="preserve">Reuters 10 月 26 日引述匿名人士稱，IDG Capital 在新加坡總部 ASMPT 的 SMT 事業洽購中較為領先，潛在交易價值可能逾 10 億美元，但尚未定案。ASMPT 於 2026 年 1 月啟動策略檢視，原始公告列出售、合資、分拆、上市或保留等多種選項。SMT 設備涉及電子板件印刷、貼片、檢測及產線軟體，應用於 AI 伺服器、光收發器及汽車電子組裝。競標報導尚不能證明設備支援與保固安排將改變。Reuters 引述上半年業務數據：SMT 營收年增 53.1% 至 38.7 億港元，接單年增 87.8% 至 69.8 億港元。上述為上半年歷史實績，新消息僅是洽購進度。未簽正式出售合約，買方、價金、監管申報及員工安排均未證實。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C26" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMT 電源、測試及設備服務供應商可追蹤正式買方與保固責任是否變更。未有已簽合約，不應推定採購或客戶合約轉移。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="194" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">力成先進封裝營收占比逾三成，第三季封測稼動率逾九成
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">力成 10 月 27 日法說公布第三季營收 253.34 億元、毛利率 24%、歸母淨利 26.12 億元；公司稱先進封裝營收占比已逾三成，第三季封裝與測試產能利用率逾九成。FOPLP 客戶驗證仍在進行，2027 年量產及新加坡投資進度均尚未確定完成。公司業務涵蓋 DRAM、NAND／eSSD 與邏輯封測，新規劃包含 FOPLP、FCBGA、2.5D／3D 異質整合及 CPO 光學引擎。這些製程分屬不同封裝產品，不應合併為已量產的同一產能。公司稱第三季大型晶片 FCBGA 已導入量產，第四季規劃更大尺寸；FOPLP 仍為 2027 年量產目標。董事長表示不排除與晶圓廠合作，但尚無正式策略聯盟合約。FOPLP 客戶認證、絕對月產能、新加坡投資金額與實際交付時點未公布。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C27" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">先進封裝設備、測試電源及量測介面供應商需要確認 FOPLP 與高階 FCBGA 實際通過客戶認證的封裝尺寸、產線設備要求及交付里程碑。第三季稼動率與 2027 年擴產計畫屬不同時點，不能直接換算設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="198" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">中華精測第三季營收 19.05 億元、淨利 5.51 億元，晶圓測試卡占前九月營收 71%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">中華精測 10 月 27 日董事會通過第三季營運成果，合併營收新台幣 19.05 億元，年增 53.4%，歸母淨利 5.51 億元，年增 100%。公司指出前九月晶圓測試卡占營收 71%、IC 測試板 21%，但下一代探針卡的個別客戶認證及產能尚未公布。晶圓探針卡、IC 測試板與高頻高速測試介面連結記憶體、AI ASIC 及先進晶圓製程的晶圓電測和後段測試。產品營收占比並非絕對生產片數。公司第一手報告另列第三季毛利率 57.3%、營業利益率約 35%，且提及 AI 客製晶片相關測試介面需求。第三季營收及獲利的 YoY 基期未於該新聞稿列同口徑絕對金額。未公布下一代探針卡客戶清單、產能稼動、產品認證周期與實際新增機台投資。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C28" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高頻測試電源與探針卡設備業者可核對實際驗證通道、訊號與電源完整性標準，以及下一代測試卡的客戶接受節點。營收結構不能直接換算設備採購或實際測試吞吐量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="178" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">穩懋第三季營收 58.59 億元，光接收元件尚在產能爬坡
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">穩懋 10 月 28 日公布第三季營收 58.59 億元、毛利率 37.4%，歸母淨利 19.3 億元；公司稱光通訊接收端 PD 元件仍處初期量產爬坡，較大規模出貨目標落在 2028 年。衛星通訊及點對點通訊需求與公司基礎設施業務相關，但並未公布各應用的獨立出貨件數。穩懋的砷化鎵 RF 和光接收元件連結衛星、光通訊及資料中心光模組等用途。產品銷售成長和前段晶圓製程擴產是不同概念。公司表示毛利率較第二季提高 9.2 個百分點，獲利季增約 98%。預估第四季營收僅低個位數增長，手機業務因記憶體價格影響仍面臨需求變化。未披露 PD 產品絕對月出貨量、合格良率、主要客戶及 2028 年產能配置。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C29" s="6">
-        <v>46323</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">射頻製程電源與光學量測供應商需確認 PD 製程良率、接收端產品類型與測試頻寬。較大出貨為遠期規劃，不能從本期集團獲利推算光模組產量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="262" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C30" s="6">
-        <v>46319</v>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="246" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">Reuters：越南 Viettel 晶圓廠尚無廠房，DUV 設備採購未定案
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">Reuters 10 月 26 日報導，越南 Viettel 在河內近郊規劃的首座晶圓廠，自 1 月動土以來尚未建起廠房，與 ASML 的 DUV 曝光機洽談亦未成交。知情人士認為 2027 年試產可能延後，但 Viettel 表示計畫仍依階段推進；目前沒有一致確認的新試產日期。越南已有 Intel、Amkor、Hana Micron 等封裝測試基地，Viettel 計畫進入前段晶圓製造，將涉及微影、沉積、蝕刻、製程電源與無塵室設施。封測產能不能替代前段晶圓廠建設。Reuters 實地查訪與衛星影像指出仍無建築，並報導越南當局先前估算建廠約 13 億美元、原定 2027 年試產及 2030 年全面運作。Viettel 回應計畫按階段推進，ASML 未確認設備合約。DUV 型號、正式採購合約、施工許可、製程技轉方及可查證的試產日期均未公布。地點：越南河內近郊 Viettel 規劃晶圓廠基地（確切工業區未披露）。</t>
           </r>
         </is>
       </c>
@@ -1404,11 +1404,11 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">晶圓製程電源、量測與廠務設備業者可追問正式機台採購、技術合約與開工許可。現地觀察和業者回覆存在差異，不能把 2027 年當作已確認的量產日期。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="198" customHeight="1">
+          <t xml:space="preserve">SMT 電源、測試及設備服務供應商可追蹤正式買方與保固責任是否變更。未有已簽合約，不應推定採購或客戶合約轉移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="194" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
@@ -1423,16 +1423,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">智原取得三星 2 奈米 GAA 雲端晶片設計專案，明年上半年擬認列收入
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">智原 10 月 27 日於法說會表示，與三星晶圓代工、聯電及記憶體供應商合作，取得美國客戶 2 奈米 GAA 雲端 AI 晶片 NRE 專案，金額為數千萬美元。公司預估 2027 年上半年開始認列首筆設計收入，但未公布精確訂單價值、客戶及晶片量產驗證日期。NRE 專案涵蓋先進製程晶片設計及多廠協作；使用三星 2 奈米代工與聯電合作，不等於聯電已可製造 2 奈米晶圓。公司第三季營收 36.64 億元，毛利率 42.5%，歸母淨利 2.79 億元；管理階層說明量產產品比重上升影響毛利率，業外評價利益亦影響淨利成長。未知客戶、製程封裝、NRE 收入精確排程及客戶晶片實際出貨量。</t>
+            <t xml:space="preserve">力成先進封裝營收占比逾三成，第三季封測稼動率逾九成
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">力成 10 月 27 日法說公布第三季營收 253.34 億元、毛利率 24%、歸母淨利 26.12 億元；公司稱先進封裝營收占比已逾三成，第三季封裝與測試產能利用率逾九成。FOPLP 客戶驗證仍在進行，2027 年量產及新加坡投資進度均尚未確定完成。公司業務涵蓋 DRAM、NAND／eSSD 與邏輯封測，新規劃包含 FOPLP、FCBGA、2.5D／3D 異質整合及 CPO 光學引擎。這些製程分屬不同封裝產品，不應合併為已量產的同一產能。公司稱第三季大型晶片 FCBGA 已導入量產，第四季規劃更大尺寸；FOPLP 仍為 2027 年量產目標。董事長表示不排除與晶圓廠合作，但尚無正式策略聯盟合約。FOPLP 客戶認證、絕對月產能、新加坡投資金額與實際交付時點未公布。</t>
           </r>
         </is>
       </c>
@@ -1441,17 +1441,239 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">先進封裝設備、測試電源及量測介面供應商需要確認 FOPLP 與高階 FCBGA 實際通過客戶認證的封裝尺寸、產線設備要求及交付里程碑。第三季稼動率與 2027 年擴產計畫屬不同時點，不能直接換算設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="198" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">中華精測第三季營收 19.05 億元、淨利 5.51 億元，晶圓測試卡占前九月營收 71%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">中華精測 10 月 27 日董事會通過第三季營運成果，合併營收新台幣 19.05 億元，年增 53.4%，歸母淨利 5.51 億元，年增 100%。公司指出前九月晶圓測試卡占營收 71%、IC 測試板 21%，但下一代探針卡的個別客戶認證及產能尚未公布。晶圓探針卡、IC 測試板與高頻高速測試介面連結記憶體、AI ASIC 及先進晶圓製程的晶圓電測和後段測試。產品營收占比並非絕對生產片數。公司第一手報告另列第三季毛利率 57.3%、營業利益率約 35%，且提及 AI 客製晶片相關測試介面需求。第三季營收及獲利的 YoY 基期未於該新聞稿列同口徑絕對金額。未公布下一代探針卡客戶清單、產能稼動、產品認證周期與實際新增機台投資。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C33" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高頻測試電源與探針卡設備業者可核對實際驗證通道、訊號與電源完整性標準，以及下一代測試卡的客戶接受節點。營收結構不能直接換算設備採購或實際測試吞吐量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="178" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">穩懋第三季營收 58.59 億元，光接收元件尚在產能爬坡
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">穩懋 10 月 28 日公布第三季營收 58.59 億元、毛利率 37.4%，歸母淨利 19.3 億元；公司稱光通訊接收端 PD 元件仍處初期量產爬坡，較大規模出貨目標落在 2028 年。衛星通訊及點對點通訊需求與公司基礎設施業務相關，但並未公布各應用的獨立出貨件數。穩懋的砷化鎵 RF 和光接收元件連結衛星、光通訊及資料中心光模組等用途。產品銷售成長和前段晶圓製程擴產是不同概念。公司表示毛利率較第二季提高 9.2 個百分點，獲利季增約 98%。預估第四季營收僅低個位數增長，手機業務因記憶體價格影響仍面臨需求變化。未披露 PD 產品絕對月出貨量、合格良率、主要客戶及 2028 年產能配置。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C34" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">射頻製程電源與光學量測供應商需確認 PD 製程良率、接收端產品類型與測試頻寬。較大出貨為遠期規劃，不能從本期集團獲利推算光模組產量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="262" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">追蹤：京元電美國子公司購德州廠址 7,935 萬美元，設備採購約 5.34 億美元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">京元電子 10 月 29 日公告，美國全資子公司 AeternZ 取得德州土地及建物，交易額約 7,935 萬美元；另陸續向鴻勁精密、EO Technics、KLA 及 TRANTEK 採購約 5.34 億美元機器與廠務設備。較早由 NVIDIA 提供的 11 億美元產能預付款是背景，2027 年 4 月量產仍為目標。京元電提供 AI GPU 和 ASIC 的測試服務；測試機台、探針、電源及散熱設備、廠務設施在晶圓製造後端形成獨立測試產線。美國新廠可作為台灣封測企業海外測試擴充，但現階段是土地、廠房與設備取得公告。公司公告土地約 117.97 萬平方英尺、建物約 48.95 萬平方英尺。這次約 6.13 億美元的廠址與設備金額為兩類採購合計，不能與 NVIDIA 的 11 億美元預付款直接相加為投資總額；付款條件與採購時間亦可能不同。德州精確地址、各設備驗收日期、最終月測試量、良率和首批客戶量產接受日期未公布。地點：美國德州 AeternZ 擬建半導體測試廠址（已取得土地與建物，街道地址未揭露）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C35" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半導體測試電源、精密量測及熱管理設備供應商需核對已購設備配置、站點上線節點及最終客戶驗收規格。設備採購額已公告，但不代表 2027 年目標產能已完成驗證。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="262" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C36" s="6">
+        <v>46319</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="246" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">Reuters：越南 Viettel 晶圓廠尚無廠房，DUV 設備採購未定案
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">Reuters 10 月 26 日報導，越南 Viettel 在河內近郊規劃的首座晶圓廠，自 1 月動土以來尚未建起廠房，與 ASML 的 DUV 曝光機洽談亦未成交。知情人士認為 2027 年試產可能延後，但 Viettel 表示計畫仍依階段推進；目前沒有一致確認的新試產日期。越南已有 Intel、Amkor、Hana Micron 等封裝測試基地，Viettel 計畫進入前段晶圓製造，將涉及微影、沉積、蝕刻、製程電源與無塵室設施。封測產能不能替代前段晶圓廠建設。Reuters 實地查訪與衛星影像指出仍無建築，並報導越南當局先前估算建廠約 13 億美元、原定 2027 年試產及 2030 年全面運作。Viettel 回應計畫按階段推進，ASML 未確認設備合約。DUV 型號、正式採購合約、施工許可、製程技轉方及可查證的試產日期均未公布。地點：越南河內近郊 Viettel 規劃晶圓廠基地（確切工業區未披露）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C37" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源、量測與廠務設備業者可追問正式機台採購、技術合約與開工許可。現地觀察和業者回覆存在差異，不能把 2027 年當作已確認的量產日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="198" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">智原取得三星 2 奈米 GAA 雲端晶片設計專案，明年上半年擬認列收入
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">智原 10 月 27 日於法說會表示，與三星晶圓代工、聯電及記憶體供應商合作，取得美國客戶 2 奈米 GAA 雲端 AI 晶片 NRE 專案，金額為數千萬美元。公司預估 2027 年上半年開始認列首筆設計收入，但未公布精確訂單價值、客戶及晶片量產驗證日期。NRE 專案涵蓋先進製程晶片設計及多廠協作；使用三星 2 奈米代工與聯電合作，不等於聯電已可製造 2 奈米晶圓。公司第三季營收 36.64 億元，毛利率 42.5%，歸母淨利 2.79 億元；管理階層說明量產產品比重上升影響毛利率，業外評價利益亦影響淨利成長。未知客戶、製程封裝、NRE 收入精確排程及客戶晶片實際出貨量。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C38" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">晶圓製程電源與先進封裝測試業者會確認實際代工場、封裝介面、矽智財驗證及後續晶片試產時程。專案 NRE 金額並非晶圓代工或設備採購支出。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="226" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="39" ht="226" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1473,22 +1695,22 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="6">
+      <c r="C39" s="6">
         <v>46323</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">晶圓製程電源、量測和先進封裝設備供應商需核對新加坡與南科分別核准的工具規格、採購及設備驗收時點。現階段只有董事會授權額與現有稼動率，尚不足以量化未來交付。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="214" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+    <row r="40" ht="214" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1510,12 +1732,86 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="6">
+      <c r="C40" s="6">
         <v>46310</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">伺服器與測試設備物流相關業者須區分轉運申報、原產地文件與出口許可要求。案件仍在調查，不能推論任何已具名供應商涉及違法行為。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="226" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">友達董事會決議以 388 億元出售台中廠予台積電，華亞廠交易取消
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">友達 10 月 29 日董事會決議將台中二期廠房、無塵室及廠務附屬設備以新台幣 388 億元售予台積電，建物權狀面積約 42.9 萬平方公尺。公司同日終止原擬售予廣達的華亞廠案，另核准增加 57.28 億元資本支出；台中廠仍在運作，交易行政程序最快 2027 年以後完成。既有廠房及廠務設施交易連結晶圓代工擴建、潔淨室改造與先進封裝空間；友達本身另研究玻璃核心基板、重布線層和光學互連元件，但目前不能視為已在買賣廠房內完成相關產線。買賣標的位於台中市西屯區安林段，交易未稅且董事會已核准。友達表示將持續使用廠房一段時間；取消華亞廠交易是因規格與交付時程未達共識。友達新核准資本支出 57.28 億元與資產出售價 388 億元屬不同財務項目。交易最終過戶日、台積電改裝用途、晶圓或先進封裝設備購置、實際投片與量產時程均未公布。地點：台灣台中市西屯區安林段，友達台中二期廠房（交易標的；仍在使用）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C41" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源、測試及廠務設備供應商需區分既有無塵室與重新改裝的機台需求，並確認正式交屋、電力容量與設備資格驗收。交易價格未揭露任何可直接採購的製程設備數量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="246" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">TSIA 估台灣 2026 年半導體產值逾 9.1 兆元，年增 40.9% 為預測
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣半導體產業協會（TSIA）理事長侯永清 10 月 29 日在新竹年會表示，2026 年台灣 IC 產值預估超過新台幣 9.1 兆元，較 2025 年成長約 40.9%。協會同時指出電力、材料、人才及國際產業合作議題；全年產值仍是預測，並非已結算的官方年度實績。協會產值估計涵蓋 IC 設計、晶圓代工及封裝測試產業，與單一公司財報或晶圓出貨片數不同。2025 年產值約 6.5 兆元為對比背景，均為報告中的整體產業口徑。TSIA 當天舉行 30 週年年會，表示現有約 220 家會員、12 個委員會，今年材料委員會也加入協會架構。協會說明支持在符合法規及安全前提下評估核能選項，並不代表能源政策已正式變更。目前未公布可查核的全年實際產值總表，材料、設備、設計與製造分項的正式全年數字及與 40.9% 預測相符的精確基期仍待確認。地點：台灣新竹市國賓大飯店（TSIA 30 週年年會活動地點，依當日媒體報導）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C42" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半導體製程電源及量測產業參與者需確認產值統計的產品分項、設備投資和供電成本資料是否分別可得。整體產業產值預測沒有直接揭露單一製造設備的需求。</t>
         </is>
       </c>
     </row>

--- a/docs/exports/week-2026-10-25.xlsx
+++ b/docs/exports/week-2026-10-25.xlsx
@@ -134,22 +134,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">記憶體、被動元件與電子材料供應
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">工研院與泰國騰輝新廠反映稀土及 PCB 材料規劃，旺宏新增 NAND／eMMC 產能、十銓新北模組廠仍待 2027 年開出。國巨 10 月 29 日公布第三季 AI 應用近兩成、MLCC 與鉭電容稼動率接近 95%，未來擴產尚待驗收。</t>
+            <t xml:space="preserve">材料、PCB 與高密度電路板擴產
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">本週先有泰國電子材料新廠啟用與記憶體擴產規劃，華通於 10 月 30 日新增 2026 至 2028 年每年資本支出逾 200 億元的規劃，用於 mSAP 與 HDI 在台灣、泰國等地擴建。各項目仍須區分已出貨與未來產能。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/24、10/26、10/27、10/28、10/29</t>
+          <t xml:space="preserve">10/24、10/26、10/27、10/28、10/29、10/30</t>
         </is>
       </c>
     </row>
@@ -168,26 +168,26 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">工廠自動化、製程量測與工業設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">本週台電復電、鴻海 AI 工廠效率量測與國研院 High-NA EUV 分析技術各為不同實績。中華精測公布探針卡擴產時程，金鞍機械啟用龍潭冷卻設備廠；研華 10 月 29 日公告第三季營收 324.4 億元及接單出貨比 1.64，數據涵蓋工業電腦與半導體設備需求。</t>
+            <t xml:space="preserve">半導體製程、廠務節電與光學測試驗證
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">工廠自動化與探針卡擴產提供不同產線進度，台積電 10 月 30 日另外公布外氣洗滌水泵由 10 降至 4 馬力的驗證成果；國發會規劃矽光子測試實驗室與 2027 年海外互認。單一泵浦節電率與未來實驗室認證不可等同已全面導入。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/25、10/26、10/27、10/28、10/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="98" customHeight="1">
+          <t xml:space="preserve">10/22、10/24、10/25、10/26、10/27、10/28、10/29、10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="82" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">03</t>
@@ -202,26 +202,26 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">資料中心供電、伺服器資金及東南亞能源零組件
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 海纜招標、馬來西亞資料中心投資意向及新加坡 1.3GW 條件性輸電核准仍未等於機房完工。台達電 29 日說明機房延遲與存貨跌價，技嘉核准 500 億元聯貸，泰國經寶精密則描述 BBU 與電源櫃機構件量產爬坡；三者屬營運說明、融資授權及產線目標。</t>
+            <t xml:space="preserve">伺服器電源、機櫃產能與跨境供應鏈
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">新加坡條件性電力進口、台達電資料中心延遲與技嘉融資均反映不同執行階段。10 月 30 日光寶科提高電源產線資本支出預算，鴻海表示 AI 機櫃產能翻倍並說明台灣、越南及北美系統整合分工，均須與實際出貨分開。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/22、10/24、10/26、10/27、10/28、10/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98" customHeight="1">
+          <t xml:space="preserve">10/22、10/24、10/26、10/27、10/28、10/29、10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="82" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">04</t>
@@ -236,26 +236,26 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">先進封裝、光通訊與半導體測試設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">力成先進封裝營收占比與精測探針卡財報為本週已公布數字，FOPLP 與 CPO 仍有產品認證階段；ASMPT SMT 出售未簽約，穩懋光接收產品在產能爬坡。京元電 10 月 29 日公布德州新測試廠土地建物及約 5.34 億美元設備取得，2027 年量產仍屬目標。</t>
+            <t xml:space="preserve">先進封裝、ASIC 與半導體測試
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">力成與中華精測公布封裝測試實績，京元電進一步採購德州測試設備。聯發科 10 月 30 日揭露首款資料中心 ASIC 已自 9 月出貨，第四季及 2027 年營收仍為預估；日月光第三季財報需依來源分級查核。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/23、10/25、10/26、10/27、10/28、10/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98" customHeight="1">
+          <t xml:space="preserve">10/23、10/25、10/26、10/27、10/28、10/29、10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="82" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
@@ -270,22 +270,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">晶圓廠房、晶片設計及產業政策
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台菲合作仍屬政策議題、越南 Viettel 晶圓廠建造與 DUV 採購尚有爭議，智原取得 2 奈米晶片設計專案，聯電核准追加擴產預算。友達 29 日決議以 388 億元出售台中廠予台積電，TSIA 同日預估全年產值逾 9.1 兆元；資產交易、研發設計、產能授權與總產值預測是不同類型資訊。</t>
+            <t xml:space="preserve">晶圓資產交易、工廠投資與產業政策
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣晶圓廠資產交易與聯電擴產授權各有不同時程，川湖 10 月 30 日另核准高雄兩座伺服器滑軌廠 197.12 億元資本支出預算。預算核准、工程簽約與真正投產仍屬不同節點。</t>
           </r>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/15、10/24、10/26、10/27、10/28、10/29</t>
+          <t xml:space="preserve">10/15、10/24、10/26、10/27、10/28、10/29、10/30</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="246" customHeight="1">
+    <row r="10" ht="178" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">08</t>
@@ -609,6 +609,43 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">華通擬連三年資本支出逾 200 億元，擴充 mSAP 與高階 HDI
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">華通 10 月 30 日表示，規劃 2026 至 2028 年每年資本支出超過 200 億元，用於台灣、中國及泰國廠區升級。公司第三季營收 225.85 億元，並稱高階 6 層以上 HDI 已量產；2027 年 mSAP 與衛星產品各 250 億元營收屬預估。基板；載板；PCB；零組件；伺服器；資料中心；投資。公司稱 6 階以上高密度板已量產，擴充 mSAP、光模組與衛星用 PCB 產能。2027 年 mSAP 與衛星業務各 250 億元營收為管理階層預估，仍有各產品驗證、客戶採購和分廠開工時間待確認。連三年資本支出及明年產品營收為公司規劃；沒有逐廠設備交貨及量產良率數據。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="6">
+        <v>46325</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器 PCB 製程電源與測試設備業者可確認 mSAP 與 HDI 產線設備、量產良率及客戶驗證階段。跨三年預算與未來營收目標尚無逐廠實際訂單資料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="246" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">薔琵颱風造成全台逾 34 萬戶曾停電，台電 10 月 24 日下午稱復電率逾 9 成
 </t>
           </r>
@@ -622,22 +659,22 @@
           </r>
         </is>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="6">
         <v>46319</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對供電設備與工業電力品質業者，應區分配電故障與廠區內備援系統失效，確認鹽塵環境下的絕緣設計、UPS 或儲能切換與實際停電波形。缺少個別工廠測量記錄，無法推定設備停機或產能損失。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="178" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="178" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -659,22 +696,22 @@
           </r>
         </is>
       </c>
-      <c r="C11" s="6">
+      <c r="C12" s="6">
         <v>46317</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工業控制電源、工業視覺測試與邊緣運算硬體供應商可確認新公司實際採用的攝影機、伺服器及邊緣裝置規格與驗收條件。尚無部署數量及工廠應用簽約資訊。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="242" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="13" ht="242" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -696,49 +733,12 @@
           </r>
         </is>
       </c>
-      <c r="C12" s="6">
+      <c r="C13" s="6">
         <v>46320</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">製程電源、UPS 和廠務監控供應商可查明各廠是否有實際電壓驟降、儲能切換或異常警報。家庭戶數復電不揭露機台開機狀態，因此不能換算設備停產或備援採購。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="146" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">鴻海與 NVIDIA 公布智慧工廠實測：排程工時減 25%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">鴻海與 NVIDIA 10 月 26 日公布特定智慧工廠流程數據，生產排程工時降低 25%，射出工程工作量降低 50%。DGX 平台的特定模型訓練速度為既有 H100 系統的 2.48 倍，尚未提供跨廠驗證。製造應用涵蓋 SMT、排程、自動化、工業量測與伺服器 AI 訓練平台。NVIDIA 指出測試以既有 H100 平台為比較基準，且 12 天處理 1 兆 Token；流程改善數據不可視為整體工廠平均成效。受測廠區、絕對工時及產線良率比較資料未公布。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C13" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製程量測與工業電源供應商可核對導入範圍及基準工時。缺乏跨廠數據，尚無法推定全面效益。</t>
         </is>
       </c>
     </row>
@@ -757,16 +757,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">JIMTOF 東京開展，公會表示有 94 家台灣廠商參展
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">日本工具機展 JIMTOF 於 10 月 26 日在東京國際展示場開展，展期至 31 日。台灣工具機公會稱有 94 家台廠參展，包含 CNC、量測與工廠自動化設備；實際成交額及設備訂單未公布。精密加工及控制設備涉及工廠自動化與半導體設備零組件製造，展出不等於簽單。主辦方確認 10 月 26 至 31 日於 Tokyo Big Sight 舉行；公會參展家數由中央社轉述。展後成交、客戶驗證及設備採購量尚未公布。地點：日本東京 Tokyo Big Sight（實際展覽場館）。</t>
+            <t xml:space="preserve">鴻海與 NVIDIA 公布智慧工廠實測：排程工時減 25%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">鴻海與 NVIDIA 10 月 26 日公布特定智慧工廠流程數據，生產排程工時降低 25%，射出工程工作量降低 50%。DGX 平台的特定模型訓練速度為既有 H100 系統的 2.48 倍，尚未提供跨廠驗證。製造應用涵蓋 SMT、排程、自動化、工業量測與伺服器 AI 訓練平台。NVIDIA 指出測試以既有 H100 平台為比較基準，且 12 天處理 1 兆 Token；流程改善數據不可視為整體工廠平均成效。受測廠區、絕對工時及產線良率比較資料未公布。</t>
           </r>
         </is>
       </c>
@@ -775,44 +775,44 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">製程量測與工業電源供應商可核對導入範圍及基準工時。缺乏跨廠數據，尚無法推定全面效益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="146" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">JIMTOF 東京開展，公會表示有 94 家台灣廠商參展
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">日本工具機展 JIMTOF 於 10 月 26 日在東京國際展示場開展，展期至 31 日。台灣工具機公會稱有 94 家台廠參展，包含 CNC、量測與工廠自動化設備；實際成交額及設備訂單未公布。精密加工及控制設備涉及工廠自動化與半導體設備零組件製造，展出不等於簽單。主辦方確認 10 月 26 至 31 日於 Tokyo Big Sight 舉行；公會參展家數由中央社轉述。展後成交、客戶驗證及設備採購量尚未公布。地點：日本東京 Tokyo Big Sight（實際展覽場館）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C15" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">設備電源與精密量測業者可核實展出技術規格與客戶驗收情況。參展家數不代表新設備訂單。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="178" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">國研院與汎銓公布 High-NA EUV 光阻奈米結構鍍膜檢測技術
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">國研院 10 月 27 日宣布，國儀中心與汎銓合作，在 High-NA EUV 與金屬氧化物光阻（MOR）曝光後，以鍍膜強化奈米結構，支援後續晶圓剖面分析。國研院稱技術已協助汎銓進入大型半導體設備與製造商供應鏈，但未公布已完成驗收的客戶、良率或量產導入規模。在高數值孔徑 EUV 微影後，金屬氧化物光阻形成的微細結構在斷面檢測前須保持形狀。樣品製備與量測結果涉及先進晶圓製程、材料分析及電子顯微技術。國研院指出，以專用鍍膜輔助強化脆弱奈米結構後，可提供後續檢測分析；公開的是研究技術突破，並未表示某製程節點已進入高良率量產。未披露可比較的缺陷率、解析度實驗結果、半導體廠認證時程及商用檢測設備採購量。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C15" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製程量測、電源及分析設備業者可檢查不同光阻與膜層的適用範圍、樣品重現性及實際客戶驗證程序。研究成功不代表已取得量產設備合約。</t>
         </is>
       </c>
     </row>
@@ -831,16 +831,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">宏偉電機稱高載重及無塵室工業電梯訂單能見度達三年
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">宏偉電機 10 月 27 日媒體交流會指出，高載重、無塵室與自動搬運用途電梯的在手訂單能見度延長至三年，今年在手訂單數量較 2025 年增加一倍。公司說半導體周邊相關出貨占比約 59%，客戶涵蓋晶圓、封測與高科技工廠，但未公布可供核對的訂單絕對金額或特定廠房。高載重、無塵室與防爆電梯可用於晶圓、封測和精密工廠的物流與廠務動線。這類建廠周邊設備不等同於曝光、蝕刻或封測機台本身。公司說今年接單出貨比持續逾一，業務涵蓋晶圓代工、半導體設備及後段封測客戶；在手訂單三年是企業口徑，並非確定三年營收額。沒有完整訂單台數、金額、交貨表、最終工地與客戶名稱，亦無可獨立驗證的在手訂單明細。</t>
+            <t xml:space="preserve">國研院與汎銓公布 High-NA EUV 光阻奈米結構鍍膜檢測技術
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">國研院 10 月 27 日宣布，國儀中心與汎銓合作，在 High-NA EUV 與金屬氧化物光阻（MOR）曝光後，以鍍膜強化奈米結構，支援後續晶圓剖面分析。國研院稱技術已協助汎銓進入大型半導體設備與製造商供應鏈，但未公布已完成驗收的客戶、良率或量產導入規模。在高數值孔徑 EUV 微影後，金屬氧化物光阻形成的微細結構在斷面檢測前須保持形狀。樣品製備與量測結果涉及先進晶圓製程、材料分析及電子顯微技術。國研院指出，以專用鍍膜輔助強化脆弱奈米結構後，可提供後續檢測分析；公開的是研究技術突破，並未表示某製程節點已進入高良率量產。未披露可比較的缺陷率、解析度實驗結果、半導體廠認證時程及商用檢測設備採購量。</t>
           </r>
         </is>
       </c>
@@ -849,17 +849,54 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">製程量測、電源及分析設備業者可檢查不同光阻與膜層的適用範圍、樣品重現性及實際客戶驗證程序。研究成功不代表已取得量產設備合約。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="178" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">宏偉電機稱高載重及無塵室工業電梯訂單能見度達三年
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">宏偉電機 10 月 27 日媒體交流會指出，高載重、無塵室與自動搬運用途電梯的在手訂單能見度延長至三年，今年在手訂單數量較 2025 年增加一倍。公司說半導體周邊相關出貨占比約 59%，客戶涵蓋晶圓、封測與高科技工廠，但未公布可供核對的訂單絕對金額或特定廠房。高載重、無塵室與防爆電梯可用於晶圓、封測和精密工廠的物流與廠務動線。這類建廠周邊設備不等同於曝光、蝕刻或封測機台本身。公司說今年接單出貨比持續逾一，業務涵蓋晶圓代工、半導體設備及後段封測客戶；在手訂單三年是企業口徑，並非確定三年營收額。沒有完整訂單台數、金額、交貨表、最終工地與客戶名稱，亦無可獨立驗證的在手訂單明細。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C17" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">工廠電力與自動搬運設備業者可核對實際交付工地、升降設備負載規格及施工驗收。訂單能見度不是已實現營收，也不能用來推估任何晶圓廠的投產日期。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="214" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="214" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -878,43 +915,6 @@
               <color rgb="FF3B4A44"/>
             </rPr>
             <t xml:space="preserve">中華精測 10 月 28 日法說指出，今年第三季高階探針卡營收接近 4 億元，約占單季營收 21%，高效能運算（HPC）業務占比 65.9%。公司表示今年 8 月產能已達 2025 年底的 2 倍，並規劃 2027 年第一季達 3 倍；這是前一日財報以外新增的產品與擴產進度。探針卡、晶圓測試板及高功率老化測試板支援 GPU、TPU、ASIC 和矽光子 CPO 的晶圓與封裝測試。高頻訊號、電力完整性和高溫耐受規格因產品而異。公司表示高階 CPU 探針卡工程驗證樣品預計 11 月出貨，量產仍以 2027 年為目標；CPO 測試介面正在與五家以上企業洽談。已核實的是公司當日陳述，不代表所有客戶驗證完成。未披露各產線絕對測試通道、測試介面月產能、已驗收客戶清單及高功率老化板出貨量。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C17" s="6">
-        <v>46323</v>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">測試電源、探針台和高功率老化設備供應商需確認 HPC 探針卡的功率密度、通道數和客戶驗收時程。倍數產能目標沒有絕對片數，無法據此推算裝機量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="194" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">金鞍機械桃園龍潭新廠啟用，布局儲冰空調及工業無人載具設備
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">義美關係企業金鞍機械 10 月 28 日在桃園龍潭啟用投資逾 10 億元的新製造大樓，預計承製逾 20 座大型離峰儲冰空調系統供集團廠區使用。公司稱義美既有龍潭廠導入儲冰空調後，尖峰用電需求下降約 25% 至 30%；此為特定廠區陳述，不代表所有資料中心或工廠能取得相同節電幅度。儲冰空調夜間製冰、白天釋冷，屬工廠空調冷負載移轉，不等同於液冷機櫃冷板、晶片散熱效能或總用電量降低。無人載具及極端環境測試為新廠另一研發方向。公司表示新大樓包含冷凍真空乾燥、儲冰系統及無人載具製造；逾 10 億元是投資額陳述，尚未拆分工程與機台支出。逾 20 座系統為計畫承製數量。未公布建置工期、各套儲冰系統額定 kW、實際耗電度數及對外客戶完成驗收數。地點：台灣桃園市龍潭區，金鞍機械製造新大樓（新廠啟用地點，詳細地址未取得）。</t>
           </r>
         </is>
       </c>
@@ -923,17 +923,54 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">測試電源、探針台和高功率老化設備供應商需確認 HPC 探針卡的功率密度、通道數和客戶驗收時程。倍數產能目標沒有絕對片數，無法據此推算裝機量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="194" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">金鞍機械桃園龍潭新廠啟用，布局儲冰空調及工業無人載具設備
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">義美關係企業金鞍機械 10 月 28 日在桃園龍潭啟用投資逾 10 億元的新製造大樓，預計承製逾 20 座大型離峰儲冰空調系統供集團廠區使用。公司稱義美既有龍潭廠導入儲冰空調後，尖峰用電需求下降約 25% 至 30%；此為特定廠區陳述，不代表所有資料中心或工廠能取得相同節電幅度。儲冰空調夜間製冰、白天釋冷，屬工廠空調冷負載移轉，不等同於液冷機櫃冷板、晶片散熱效能或總用電量降低。無人載具及極端環境測試為新廠另一研發方向。公司表示新大樓包含冷凍真空乾燥、儲冰系統及無人載具製造；逾 10 億元是投資額陳述，尚未拆分工程與機台支出。逾 20 座系統為計畫承製數量。未公布建置工期、各套儲冰系統額定 kW、實際耗電度數及對外客戶完成驗收數。地點：台灣桃園市龍潭區，金鞍機械製造新大樓（新廠啟用地點，詳細地址未取得）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C19" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">工業冷卻、壓縮機驅動及電力控制供應商需確認儲冰容量、負載曲線和峰時需量計算方式。個別廠區降低尖峰負載並不等於所有製造或機房情境可直接複製。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="214" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="214" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -955,53 +992,16 @@
           </r>
         </is>
       </c>
-      <c r="C19" s="6">
+      <c r="C20" s="6">
         <v>46324</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工業量測、精密電源與半導體設備供應商需對照研華的不同應用產品、區域接單結構與實際交貨。接單出貨比提供需求指標，仍需出貨明細才可確認最終設備使用情境。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="310" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">MViSTA 海纜開發商稱將於 10 月決標，規劃串聯東南亞四國與越南資料中心
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">Reuters 10 月 22 日引述越南 Stavian 旗下 MViSTA 開發主管表示，連接馬來西亞、越南、新加坡及泰國的 16 對光纖海底電纜，預估長 2,500 公里、成本約 4 億美元，將在日本 NEC 與法國 Alcatel Submarine Networks 間選擇供應商，目標 2028 年底啟用。工程尚未決標，越南資料中心園區也仍處可行性研究階段。海纜可提供跨國資料中心及雲端流量互連；相關股東含越南 Stavian、日本 Midas Capital 與馬來西亞 OMS Group 子公司 LitUp Network，後者預定負責鋪設工程。海纜容量、陸上機房電力、光纖上線及雲端承租並非相同進度。Reuters 引述開發商稱仍待招標定案；USTDA 於 9 月 23 日公告，資助越南胡志明市 Stavian Digital Park 的供電、散熱與連接設施可行性研究，該研究並不等於園區已取得建廠融資。開發商對供應商排除條件的早期發言之後已澄清為個人看法，不應作為採購禁令。未公布最終海纜供應商、確定合約價格、路線許可、登陸站、測試容量與越南資料中心最終投資額；4 億美元及 2028 年底均為預估。地點：計畫連接越南、馬來西亞、新加坡及泰國；登陸站點未公布。關聯機房園區規劃位於越南胡志明市。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C20" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="294" customHeight="1">
+    <row r="21" ht="162" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -1016,25 +1016,25 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">馬國總理披露 500 億美元 AI 與資料中心投資意向，未公告專案核准
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">馬來西亞總理安華 10 月 24 日在馬六甲表示，一名國際投資人於視訊會議中提出約 500 億美元的 AI、新科技與資料中心投資意向，地點包括砂拉越古晉及馬來西亞半島。新加坡《商業時報》10 月 25 日將投資人指為 SoftBank 創辦人孫正義，但尚無 SoftBank 正式投資承諾、核准專案、供電容量或動工日期公告。大型資料中心計畫涉及伺服器與機櫃 ODM、UPS 與電力轉換、冷卻設備、變電系統和光纖互連。安華亦談及半導體人才及向較高附加價值技術環節發展，但並未宣布半導體晶圓廠新案。馬來西亞國家通訊社 Bernama 記錄安華於 10 月 24 日公開發言，投資人意向來自前一週二的視訊會議。新加坡《商業時報》 25 日補充投資人姓名，並指 SoftBank 尚未回應置評要求；兩篇報導均未取得具體合約或許可文件。500 億美元是總理轉述的跨領域投資意向，沒有逐年撥款表、各州配置或已支付金額，不能計入核准 FDI、已建置機房容量或設備採購。投資人正式企業公告、土地權利、電網併接與需量、冷卻用水、專案融資、機房建照及交付時程尚未公布。地點：馬來西亞砂拉越州古晉及馬來西亞半島（擬投資地區，無已核實工地）；發言活動於馬六甲 Hang Jebat 運動場。</t>
+            <t xml:space="preserve">台積電外氣空調洗滌改裝驗證，水泵功率由 10 馬力降至 4 馬力
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台積電 10 月 30 日 ESG 資訊說明，外氣空調箱洗滌技術改裝後，水泵由 10 馬力降至 4 馬力，該項電力減幅達 60%；截至 10 月已在晶圓六廠與先進封測七廠完成運轉驗證。該百分比對應特定水泵，不能視為整座晶圓廠節電 60%。晶圓；封測；設備；供電；電力；工廠。新型外氣空調箱使用濕膜板及重力水流取代馬達加壓，台積電表示晶圓六廠與先進封測七廠已完成驗證。節電 60% 是這一款水泵的功率變化，並非晶圓製造用電量的減幅。驗證限於兩座指名廠，沒有全廠電量基準，亦未公布其他 12 吋廠的全面導入日期。</t>
           </r>
         </is>
       </c>
       <c r="C21" s="6">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
+          <t xml:space="preserve">廠務電源與工業控制設備業者會關注改裝後的泵浦負載、控制器規格及維護條件。特定設備節電率不能直接推估所有晶圓廠總電量變化。</t>
         </is>
       </c>
     </row>
@@ -1053,6 +1053,117 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">國發會規劃矽光子驗證實驗室，2027 年擬與海外互認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">國發會主委 10 月 30 日表示，將建置矽光子測試驗證實驗室，目標 2027 年與海外實驗室交互認證，2028 年爭取通過 OIF 認證。現行產品送海外驗證歷時 6 個月至 2 年是官員說法，尚無新實驗室正式啟用與驗收資料。CPO；矽光子；測試；封裝；晶圓；政策。政府說明目前矽光子產品送海外驗證需約半年至兩年，擬建立國內測試驗證設施以支援 CPO 和高速光互連。海外實驗室互認及 OIF 認證均為政策目標，沒有已完成的國內認證成果。實驗室地址、預算、設備清單、互認條件與實際認證均待確認。地點：台灣台北市，矽光子驗證實驗室規劃中（實際場址未公布）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C22" s="6">
+        <v>46325</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">光學量測與半導體測試企業可確認國內實驗室的設備項目、測試規範和跨境互認條件。未來認證時間點還無法視為已完成商用驗證。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="310" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">MViSTA 海纜開發商稱將於 10 月決標，規劃串聯東南亞四國與越南資料中心
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">Reuters 10 月 22 日引述越南 Stavian 旗下 MViSTA 開發主管表示，連接馬來西亞、越南、新加坡及泰國的 16 對光纖海底電纜，預估長 2,500 公里、成本約 4 億美元，將在日本 NEC 與法國 Alcatel Submarine Networks 間選擇供應商，目標 2028 年底啟用。工程尚未決標，越南資料中心園區也仍處可行性研究階段。海纜可提供跨國資料中心及雲端流量互連；相關股東含越南 Stavian、日本 Midas Capital 與馬來西亞 OMS Group 子公司 LitUp Network，後者預定負責鋪設工程。海纜容量、陸上機房電力、光纖上線及雲端承租並非相同進度。Reuters 引述開發商稱仍待招標定案；USTDA 於 9 月 23 日公告，資助越南胡志明市 Stavian Digital Park 的供電、散熱與連接設施可行性研究，該研究並不等於園區已取得建廠融資。開發商對供應商排除條件的早期發言之後已澄清為個人看法，不應作為採購禁令。未公布最終海纜供應商、確定合約價格、路線許可、登陸站、測試容量與越南資料中心最終投資額；4 億美元及 2028 年底均為預估。地點：計畫連接越南、馬來西亞、新加坡及泰國；登陸站點未公布。關聯機房園區規劃位於越南胡志明市。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C23" s="6">
+        <v>46317</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對資料中心電源、液冷與量測業者，需將海纜招標時程、越南園區可行性研究和機房實際供電容量分開追蹤。尚缺確定登陸站、雲端承租人、電力容量契約與施工許可，無法估算設備裝機時點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="294" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">馬國總理披露 500 億美元 AI 與資料中心投資意向，未公告專案核准
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞總理安華 10 月 24 日在馬六甲表示，一名國際投資人於視訊會議中提出約 500 億美元的 AI、新科技與資料中心投資意向，地點包括砂拉越古晉及馬來西亞半島。新加坡《商業時報》10 月 25 日將投資人指為 SoftBank 創辦人孫正義，但尚無 SoftBank 正式投資承諾、核准專案、供電容量或動工日期公告。大型資料中心計畫涉及伺服器與機櫃 ODM、UPS 與電力轉換、冷卻設備、變電系統和光纖互連。安華亦談及半導體人才及向較高附加價值技術環節發展，但並未宣布半導體晶圓廠新案。馬來西亞國家通訊社 Bernama 記錄安華於 10 月 24 日公開發言，投資人意向來自前一週二的視訊會議。新加坡《商業時報》 25 日補充投資人姓名，並指 SoftBank 尚未回應置評要求；兩篇報導均未取得具體合約或許可文件。500 億美元是總理轉述的跨領域投資意向，沒有逐年撥款表、各州配置或已支付金額，不能計入核准 FDI、已建置機房容量或設備採購。投資人正式企業公告、土地權利、電網併接與需量、冷卻用水、專案融資、機房建照及交付時程尚未公布。地點：馬來西亞砂拉越州古晉及馬來西亞半島（擬投資地區，無已核實工地）；發言活動於馬六甲 Hang Jebat 運動場。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C24" s="6">
+        <v>46319</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">資料中心電源轉換、UPS、電力品質及液冷廠商，需要先核對項目地點、兆瓦級實際供電許可、客戶認證與採購節點。單一意向總額缺乏場址及供應商分配資訊，無法推算設備出貨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="162" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">新加坡有條件核准跨境進口電力 1.3GW，目標 2035 年開始供應
 </t>
           </r>
@@ -1066,22 +1177,22 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="6">
+      <c r="C25" s="6">
         <v>46321</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">電力轉換與機房供電設備業者可核對輸配電規格、電池配置及購電合約。尚無施工與融資定案資料，無法推估供應商設備交付。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="194" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="26" ht="194" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1103,22 +1214,22 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="6">
+      <c r="C26" s="6">
         <v>46322</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">智慧工廠電源、控制與測試系統業者可核對移轉設備類別、既有與新增裝機占比以及驗收階段。關係人交易價值不等於泰國廠新增加的生產能力。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="198" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="27" ht="198" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1140,123 +1251,12 @@
           </r>
         </is>
       </c>
-      <c r="C24" s="6">
+      <c r="C27" s="6">
         <v>46323</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">電源轉換與工業量測供應商應分清集團財報與資料中心電源各產品的實際交付量，並核對後續法說是否揭露新款產品驗收。財報數值不能直接推算新增機櫃設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="210" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">是方第三季營收 10.77 億元，聯雲 LY2 年底進駐率目標八成
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">是方 10 月 28 日公布第三季營收 10.77 億元、毛利率 51.5%、稅後淨利 3.32 億元。公司說聯雲 LY2 資料中心客戶進駐率逐季提高，目標年底達八成；虎尾 AI 資料中心已於 10 月 20 日動土，規劃 2028 年下半年營運，但沒有公布已完成裝機的 IT 負載或新增機櫃數。資料中心需求涉及機房配電、UPS、散熱及跨境網路連接。進駐率是租用或客戶使用比例，不能直接視為機房滿載電力或 GPU 運算使用率。管理層指出今年起 LY2 折舊費用完整認列，第三季毛利率仍高於上半年 48.55% 的水準；年末進駐率八成是目標，尚非 10 月 28 日的實際占用率。未披露最新實際進駐率、總可用機架、已供電 MW、冷卻密度及虎尾機房核定容量。地點：台灣台北市聯雲 LY2 資料中心（已營運機房）；雲林縣虎尾鎮另有規劃中的 AI 機房工地。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C25" s="6">
-        <v>46323</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">機房電源、UPS 和液冷業者需確認進駐率定義、實際獲供電的機架和每機櫃功率。進駐率八成為管理層預期，尚不能換算已採購設備數量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="198" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">追蹤：台達電說明資料中心建置延遲及缺料，第三季存貨跌價約占營收 1.7%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台達電董事長鄭平 10 月 29 日法說表示，第三季部分資料中心建置延遲、供應鏈長短料等因素導致存貨跌價損失，金額約占總營收 1.7%。公司預期第四季營收高於第三季，但供電設備、人力、材料和地方審批等問題仍會影響大型資料中心交付速度。資料中心電源、HVDC、UPS、變電及散熱系統依機房土建與電網可用時間交付，設備製造商的已備料庫存不代表最終客戶已完成機櫃部署。第三季歸母淨利 234.95 億元是 10 月 28 日已公布的歷史實績；29 日新增的是管理階層對存貨跌價、材料匹配及機房建置障礙的解釋。存貨跌價占營收 1.7% 亦不可視為 1.7% 的設備故障率。尚未提供逐機房延遲天數、受影響客戶、第四季實際存貨迴轉額或各電源產品的獨立訂單量。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C26" s="6">
-        <v>46324</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">資料中心供電、電源轉換和量測產品供應商需核對客戶電網就緒、工程人力及設備交付驗收節點。存貨損失反映部分時程與供應配置問題，不能直接等同設備品質不良。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="178" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">技嘉董事會通過 500 億元聯貸，資金供償債及 AI 產品營運週轉
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">技嘉 10 月 29 日董事會通過與台灣銀行、兆豐、華南及國泰世華等主辦銀行團簽訂新台幣 500 億元聯合授信合約，資金用途包含償還金融機構借款及中期週轉。公司指出 2027 年 AI 產品備料與採購需求，但授信額度並非已動用資金、已簽客戶訂單或新增營收。技嘉製造主機板、GPU 系統及 AI 伺服器與機櫃設備，營運週轉金可涉及晶片、記憶體及整機備料。銀行聯貸核准本身不代表特定伺服器型號或零組件已投入生產。董事會核准聯合授信條件，銀行包括台灣銀行、兆豐國際、華南及國泰世華。公司未在公告中細分 AI 採購與債務償還分配比例，也沒有揭露實際提款金額。貸款動用率、實際 AI 伺服器物料採購金額、客戶與交機數量、借款成本及具體備貨月份未公布。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C27" s="6">
-        <v>46324</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">伺服器電源、機櫃配電及電子測試設備供應商應核對實際採購排程與客戶驗收條件。聯貸額度無法直接換算為機櫃數、電源模組訂單或晶片出貨。</t>
         </is>
       </c>
     </row>
@@ -1275,6 +1275,117 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">是方第三季營收 10.77 億元，聯雲 LY2 年底進駐率目標八成
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">是方 10 月 28 日公布第三季營收 10.77 億元、毛利率 51.5%、稅後淨利 3.32 億元。公司說聯雲 LY2 資料中心客戶進駐率逐季提高，目標年底達八成；虎尾 AI 資料中心已於 10 月 20 日動土，規劃 2028 年下半年營運，但沒有公布已完成裝機的 IT 負載或新增機櫃數。資料中心需求涉及機房配電、UPS、散熱及跨境網路連接。進駐率是租用或客戶使用比例，不能直接視為機房滿載電力或 GPU 運算使用率。管理層指出今年起 LY2 折舊費用完整認列，第三季毛利率仍高於上半年 48.55% 的水準；年末進駐率八成是目標，尚非 10 月 28 日的實際占用率。未披露最新實際進駐率、總可用機架、已供電 MW、冷卻密度及虎尾機房核定容量。地點：台灣台北市聯雲 LY2 資料中心（已營運機房）；雲林縣虎尾鎮另有規劃中的 AI 機房工地。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C28" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機房電源、UPS 和液冷業者需確認進駐率定義、實際獲供電的機架和每機櫃功率。進駐率八成為管理層預期，尚不能換算已採購設備數量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="198" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">追蹤：台達電說明資料中心建置延遲及缺料，第三季存貨跌價約占營收 1.7%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台達電董事長鄭平 10 月 29 日法說表示，第三季部分資料中心建置延遲、供應鏈長短料等因素導致存貨跌價損失，金額約占總營收 1.7%。公司預期第四季營收高於第三季，但供電設備、人力、材料和地方審批等問題仍會影響大型資料中心交付速度。資料中心電源、HVDC、UPS、變電及散熱系統依機房土建與電網可用時間交付，設備製造商的已備料庫存不代表最終客戶已完成機櫃部署。第三季歸母淨利 234.95 億元是 10 月 28 日已公布的歷史實績；29 日新增的是管理階層對存貨跌價、材料匹配及機房建置障礙的解釋。存貨跌價占營收 1.7% 亦不可視為 1.7% 的設備故障率。尚未提供逐機房延遲天數、受影響客戶、第四季實際存貨迴轉額或各電源產品的獨立訂單量。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">資料中心供電、電源轉換和量測產品供應商需核對客戶電網就緒、工程人力及設備交付驗收節點。存貨損失反映部分時程與供應配置問題，不能直接等同設備品質不良。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="178" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">技嘉董事會通過 500 億元聯貸，資金供償債及 AI 產品營運週轉
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">技嘉 10 月 29 日董事會通過與台灣銀行、兆豐、華南及國泰世華等主辦銀行團簽訂新台幣 500 億元聯合授信合約，資金用途包含償還金融機構借款及中期週轉。公司指出 2027 年 AI 產品備料與採購需求，但授信額度並非已動用資金、已簽客戶訂單或新增營收。技嘉製造主機板、GPU 系統及 AI 伺服器與機櫃設備，營運週轉金可涉及晶片、記憶體及整機備料。銀行聯貸核准本身不代表特定伺服器型號或零組件已投入生產。董事會核准聯合授信條件，銀行包括台灣銀行、兆豐國際、華南及國泰世華。公司未在公告中細分 AI 採購與債務償還分配比例，也沒有揭露實際提款金額。貸款動用率、實際 AI 伺服器物料採購金額、客戶與交機數量、借款成本及具體備貨月份未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C30" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伺服器電源、機櫃配電及電子測試設備供應商應核對實際採購排程與客戶驗收條件。聯貸額度無法直接換算為機櫃數、電源模組訂單或晶片出貨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="210" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">泰國經寶精密切入電源櫃及 BBU 機構件，第四季大規模量產為公司目標
 </t>
           </r>
@@ -1288,22 +1399,96 @@
           </r>
         </is>
       </c>
-      <c r="C28" s="6">
+      <c r="C31" s="6">
         <v>46324</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">機櫃供電、BBU 及工業電源供應商需核對機構件的散熱、絕緣、EMI 和可靠度驗收。公司提及量產規劃，但未揭露交付基數，不應換算成資料中心電源實際部署。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="242" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="32" ht="178" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">光寶科上修資本支出至 197 億元，高功率電源新品進入量產
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">光寶科 10 月 30 日公布第三季營收 574 億元、稅後純益 74 億元，並再度上修 2026 年資本支出預算至 197 億元。公司稱 8.5kW ASIC 電源及 BBU 進入量產，800VDC Power Rack 第四季擬出貨樣機；越南新廠規劃 11 月開幕。電源；供電；BBU；伺服器；資料中心；測試；工廠。公司說明前九月已投入約 131 億元資本支出，與本次全年 197 億元預算屬不同口徑。新加坡及北美等海外據點之外，越南新廠預計 11 月開幕，美國德州廠以 2027 年第二季營運為目標。197 億元是全年資本支出預算，與前九月已支付約 131 億元不同；越南廠和美國廠尚待後續啟用。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C32" s="6">
+        <v>46325</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高功率電源及資料中心供電企業會關注 8.5kW 電源、BBU 與 800VDC 樣機的可靠度測試及驗收日期。資本支出預算不等於已交付產品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="178" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">鴻海稱 AI 機櫃每週產能由千台翻倍，台越與北美分工整合
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">鴻海 10 月 30 日科技日指出，AI 機櫃每週產能一年來由約 1,000 台翻倍，並在台灣、越南及美國與墨西哥建立不同層級系統整合流程。NVIDIA 說明超過 10 座廠參與 Vera Rubin 平台製造；實際客戶交機量與跨廠有效產出尚未披露。ODM；伺服器；整機；CPO；供電；散熱；資料中心。公司說明 Level 1 至 Level 12 的生產分工，台灣與越南製造部分零組件，北美負責更高層級系統整合。NVIDIA 指出超過十座工廠參與 Vera Rubin 平台生產，但未公布逐廠驗收量與對外交付。翻倍是公司公布的每週產能變化，並非當週實際出貨；Vera Rubin 仍在生產建置階段。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C33" s="6">
+        <v>46325</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機櫃電源、散熱與光通訊測試業者可確認 Level 11、12 整合規格及 CPO 製程驗收。每週產能倍增不等於實際交付與客戶接受量同步倍增。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="242" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1325,22 +1510,22 @@
           </r>
         </is>
       </c>
-      <c r="C29" s="6">
+      <c r="C34" s="6">
         <v>46318</v>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對精密製造量測、光學封裝設備與資料中心電源商而言，值得核實 EBO 接頭良率、客戶認證和 CPO 光互連產品實際產量。私募資金入帳與既有光學營收並不能直接推算新模組設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="258" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="35" ht="258" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1362,22 +1547,22 @@
           </r>
         </is>
       </c>
-      <c r="C30" s="6">
+      <c r="C35" s="6">
         <v>46320</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">伺服器、機櫃及半導體設備物流與工業電源供應商，可釐清空運需求反映急單、正常補貨或專用航班，並分別核對運價與燃料因素。貨運營收未區分 AI 出貨占比，尚不足以推算設備產量。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="214" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="36" ht="214" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1399,22 +1584,22 @@
           </r>
         </is>
       </c>
-      <c r="C31" s="6">
+      <c r="C36" s="6">
         <v>46321</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">SMT 電源、測試及設備服務供應商可追蹤正式買方與保固責任是否變更。未有已簽合約，不應推定採購或客戶合約轉移。</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="194" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+    <row r="37" ht="194" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1436,197 +1621,12 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="6">
+      <c r="C37" s="6">
         <v>46322</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">先進封裝設備、測試電源及量測介面供應商需要確認 FOPLP 與高階 FCBGA 實際通過客戶認證的封裝尺寸、產線設備要求及交付里程碑。第三季稼動率與 2027 年擴產計畫屬不同時點，不能直接換算設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="198" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">中華精測第三季營收 19.05 億元、淨利 5.51 億元，晶圓測試卡占前九月營收 71%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">中華精測 10 月 27 日董事會通過第三季營運成果，合併營收新台幣 19.05 億元，年增 53.4%，歸母淨利 5.51 億元，年增 100%。公司指出前九月晶圓測試卡占營收 71%、IC 測試板 21%，但下一代探針卡的個別客戶認證及產能尚未公布。晶圓探針卡、IC 測試板與高頻高速測試介面連結記憶體、AI ASIC 及先進晶圓製程的晶圓電測和後段測試。產品營收占比並非絕對生產片數。公司第一手報告另列第三季毛利率 57.3%、營業利益率約 35%，且提及 AI 客製晶片相關測試介面需求。第三季營收及獲利的 YoY 基期未於該新聞稿列同口徑絕對金額。未公布下一代探針卡客戶清單、產能稼動、產品認證周期與實際新增機台投資。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C33" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高頻測試電源與探針卡設備業者可核對實際驗證通道、訊號與電源完整性標準，以及下一代測試卡的客戶接受節點。營收結構不能直接換算設備採購或實際測試吞吐量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="178" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">穩懋第三季營收 58.59 億元，光接收元件尚在產能爬坡
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">穩懋 10 月 28 日公布第三季營收 58.59 億元、毛利率 37.4%，歸母淨利 19.3 億元；公司稱光通訊接收端 PD 元件仍處初期量產爬坡，較大規模出貨目標落在 2028 年。衛星通訊及點對點通訊需求與公司基礎設施業務相關，但並未公布各應用的獨立出貨件數。穩懋的砷化鎵 RF 和光接收元件連結衛星、光通訊及資料中心光模組等用途。產品銷售成長和前段晶圓製程擴產是不同概念。公司表示毛利率較第二季提高 9.2 個百分點，獲利季增約 98%。預估第四季營收僅低個位數增長，手機業務因記憶體價格影響仍面臨需求變化。未披露 PD 產品絕對月出貨量、合格良率、主要客戶及 2028 年產能配置。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C34" s="6">
-        <v>46323</v>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">射頻製程電源與光學量測供應商需確認 PD 製程良率、接收端產品類型與測試頻寬。較大出貨為遠期規劃，不能從本期集團獲利推算光模組產量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="262" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">追蹤：京元電美國子公司購德州廠址 7,935 萬美元，設備採購約 5.34 億美元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">京元電子 10 月 29 日公告，美國全資子公司 AeternZ 取得德州土地及建物，交易額約 7,935 萬美元；另陸續向鴻勁精密、EO Technics、KLA 及 TRANTEK 採購約 5.34 億美元機器與廠務設備。較早由 NVIDIA 提供的 11 億美元產能預付款是背景，2027 年 4 月量產仍為目標。京元電提供 AI GPU 和 ASIC 的測試服務；測試機台、探針、電源及散熱設備、廠務設施在晶圓製造後端形成獨立測試產線。美國新廠可作為台灣封測企業海外測試擴充，但現階段是土地、廠房與設備取得公告。公司公告土地約 117.97 萬平方英尺、建物約 48.95 萬平方英尺。這次約 6.13 億美元的廠址與設備金額為兩類採購合計，不能與 NVIDIA 的 11 億美元預付款直接相加為投資總額；付款條件與採購時間亦可能不同。德州精確地址、各設備驗收日期、最終月測試量、良率和首批客戶量產接受日期未公布。地點：美國德州 AeternZ 擬建半導體測試廠址（已取得土地與建物，街道地址未揭露）。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C35" s="6">
-        <v>46324</v>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">半導體測試電源、精密量測及熱管理設備供應商需核對已購設備配置、站點上線節點及最終客戶驗收規格。設備採購額已公告，但不代表 2027 年目標產能已完成驗證。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="262" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C36" s="6">
-        <v>46319</v>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="246" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">Reuters：越南 Viettel 晶圓廠尚無廠房，DUV 設備採購未定案
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">Reuters 10 月 26 日報導，越南 Viettel 在河內近郊規劃的首座晶圓廠，自 1 月動土以來尚未建起廠房，與 ASML 的 DUV 曝光機洽談亦未成交。知情人士認為 2027 年試產可能延後，但 Viettel 表示計畫仍依階段推進；目前沒有一致確認的新試產日期。越南已有 Intel、Amkor、Hana Micron 等封裝測試基地，Viettel 計畫進入前段晶圓製造，將涉及微影、沉積、蝕刻、製程電源與無塵室設施。封測產能不能替代前段晶圓廠建設。Reuters 實地查訪與衛星影像指出仍無建築，並報導越南當局先前估算建廠約 13 億美元、原定 2027 年試產及 2030 年全面運作。Viettel 回應計畫按階段推進，ASML 未確認設備合約。DUV 型號、正式採購合約、施工許可、製程技轉方及可查證的試產日期均未公布。地點：越南河內近郊 Viettel 規劃晶圓廠基地（確切工業區未披露）。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C37" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">晶圓製程電源、量測與廠務設備業者可追問正式機台採購、技術合約與開工許可。現地觀察和業者回覆存在差異，不能把 2027 年當作已確認的量產日期。</t>
         </is>
       </c>
     </row>
@@ -1645,16 +1645,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">智原取得三星 2 奈米 GAA 雲端晶片設計專案，明年上半年擬認列收入
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">智原 10 月 27 日於法說會表示，與三星晶圓代工、聯電及記憶體供應商合作，取得美國客戶 2 奈米 GAA 雲端 AI 晶片 NRE 專案，金額為數千萬美元。公司預估 2027 年上半年開始認列首筆設計收入，但未公布精確訂單價值、客戶及晶片量產驗證日期。NRE 專案涵蓋先進製程晶片設計及多廠協作；使用三星 2 奈米代工與聯電合作，不等於聯電已可製造 2 奈米晶圓。公司第三季營收 36.64 億元，毛利率 42.5%，歸母淨利 2.79 億元；管理階層說明量產產品比重上升影響毛利率，業外評價利益亦影響淨利成長。未知客戶、製程封裝、NRE 收入精確排程及客戶晶片實際出貨量。</t>
+            <t xml:space="preserve">中華精測第三季營收 19.05 億元、淨利 5.51 億元，晶圓測試卡占前九月營收 71%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">中華精測 10 月 27 日董事會通過第三季營運成果，合併營收新台幣 19.05 億元，年增 53.4%，歸母淨利 5.51 億元，年增 100%。公司指出前九月晶圓測試卡占營收 71%、IC 測試板 21%，但下一代探針卡的個別客戶認證及產能尚未公布。晶圓探針卡、IC 測試板與高頻高速測試介面連結記憶體、AI ASIC 及先進晶圓製程的晶圓電測和後段測試。產品營收占比並非絕對生產片數。公司第一手報告另列第三季毛利率 57.3%、營業利益率約 35%，且提及 AI 客製晶片相關測試介面需求。第三季營收及獲利的 YoY 基期未於該新聞稿列同口徑絕對金額。未公布下一代探針卡客戶清單、產能稼動、產品認證周期與實際新增機台投資。</t>
           </r>
         </is>
       </c>
@@ -1663,11 +1663,11 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">晶圓製程電源與先進封裝測試業者會確認實際代工場、封裝介面、矽智財驗證及後續晶片試產時程。專案 NRE 金額並非晶圓代工或設備採購支出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="226" customHeight="1">
+          <t xml:space="preserve">高頻測試電源與探針卡設備業者可核對實際驗證通道、訊號與電源完整性標準，以及下一代測試卡的客戶接受節點。營收結構不能直接換算設備採購或實際測試吞吐量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="178" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">37</t>
@@ -1682,16 +1682,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">聯電董事會追加約 32 億美元擴產預算，指向新加坡與南科
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">聯電 10 月 28 日董事會通過約 32 億美元追加擴產預算，公司表示將用於加快新加坡與南科擴建進度，但未提供新產能逐月開出日期。第三季合併營收 742.4 億元、毛利率 34%，12 吋約當晶圓出貨逾 120 萬片，產能利用率達 92%。晶圓代工產能包括成熟節點與 22／28 奈米特殊製程，涉及電源管理 IC、連接晶片、矽光子和工業控制。追加核准資金不等於設備已裝機或支出已發生。聯電原定 2026 年資本支出約 20 億美元，此次為董事會另外核准的擴產預算，不應與季度費用混為一談。公司預估第四季出貨季增 1% 至 3%、稼動率約 91% 至 93%，2027 年平均售價年增 10% 為管理階層預期，非已簽實績。沒有分廠核定支出配置、採購設備清單、投片擴增量、實際動工或轉量產日期；遠期平均售價及 AI 營收占比均為預測。地點：台灣台南科學園區及新加坡既有與規劃廠區（擴產所在區域，未指定新增廠房地址）。</t>
+            <t xml:space="preserve">穩懋第三季營收 58.59 億元，光接收元件尚在產能爬坡
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">穩懋 10 月 28 日公布第三季營收 58.59 億元、毛利率 37.4%，歸母淨利 19.3 億元；公司稱光通訊接收端 PD 元件仍處初期量產爬坡，較大規模出貨目標落在 2028 年。衛星通訊及點對點通訊需求與公司基礎設施業務相關，但並未公布各應用的獨立出貨件數。穩懋的砷化鎵 RF 和光接收元件連結衛星、光通訊及資料中心光模組等用途。產品銷售成長和前段晶圓製程擴產是不同概念。公司表示毛利率較第二季提高 9.2 個百分點，獲利季增約 98%。預估第四季營收僅低個位數增長，手機業務因記憶體價格影響仍面臨需求變化。未披露 PD 產品絕對月出貨量、合格良率、主要客戶及 2028 年產能配置。</t>
           </r>
         </is>
       </c>
@@ -1700,17 +1700,276 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">射頻製程電源與光學量測供應商需確認 PD 製程良率、接收端產品類型與測試頻寬。較大出貨為遠期規劃，不能從本期集團獲利推算光模組產量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="262" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">追蹤：京元電美國子公司購德州廠址 7,935 萬美元，設備採購約 5.34 億美元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">京元電子 10 月 29 日公告，美國全資子公司 AeternZ 取得德州土地及建物，交易額約 7,935 萬美元；另陸續向鴻勁精密、EO Technics、KLA 及 TRANTEK 採購約 5.34 億美元機器與廠務設備。較早由 NVIDIA 提供的 11 億美元產能預付款是背景，2027 年 4 月量產仍為目標。京元電提供 AI GPU 和 ASIC 的測試服務；測試機台、探針、電源及散熱設備、廠務設施在晶圓製造後端形成獨立測試產線。美國新廠可作為台灣封測企業海外測試擴充，但現階段是土地、廠房與設備取得公告。公司公告土地約 117.97 萬平方英尺、建物約 48.95 萬平方英尺。這次約 6.13 億美元的廠址與設備金額為兩類採購合計，不能與 NVIDIA 的 11 億美元預付款直接相加為投資總額；付款條件與採購時間亦可能不同。德州精確地址、各設備驗收日期、最終月測試量、良率和首批客戶量產接受日期未公布。地點：美國德州 AeternZ 擬建半導體測試廠址（已取得土地與建物，街道地址未揭露）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C40" s="6">
+        <v>46324</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半導體測試電源、精密量測及熱管理設備供應商需核對已購設備配置、站點上線節點及最終客戶驗收規格。設備採購額已公告，但不代表 2027 年目標產能已完成驗證。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="162" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">聯發科 AI ASIC 出貨與營收指引
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">聯發科 10 月 30 日表示首款資料中心 ASIC 已於 9 月開始小量出貨，預估第四季相關營收 25 億美元、2027 年 160 億美元。公司第三季營收 1,680.58 億元、毛利率 46.3%，2028 年第一季量產第二款 ASIC 仍是目標。晶片設計；晶圓；先進封裝；資料中心。晶片設計及資料中心加速器設計涉及晶圓代工、先進封裝、載板與高速互連。公司另提及第二個 ASIC 專案與新客戶，尚未揭露客戶名稱、晶圓及封裝採購量。現有 ASIC 已開始出貨，未來營收、客戶市占及第二款晶片量產仍屬管理層預估。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C41" s="6">
+        <v>46325</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半導體製程電源與測試儀器供應商可核對 ASIC 使用的晶圓廠、封裝規格及客戶量產驗收節點。未來營收指引尚不能直接換算設備採購量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="146" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">日月光投控公布第三季封測營收及產能利用率
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">日月光投控 10 月 30 日揭露第三季合併營收約 2,442 億元，並表示封裝、測試及材料產能在部分高階業務接近滿載；電子代工服務占比亦需與封測收入區分。已公布第三季數值不應與全年成長指引或市場分析師預測混用。封裝；封測；測試；材料；伺服器。日月光的合併營收涵蓋封裝、測試、材料及電子製造服務，不能將集團營收全部視為先進封裝收入。二手報導提及產能吃緊，但未提供按產線的絕對設備或測試通道數。目前來源是二手媒體摘要，尚待原始公司報表確認分項營收與滿載程度。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C42" s="6">
+        <v>46325</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">封裝測試設備與精密電源業者可追問各產品產線稼動率及客戶訂單驗收細節。目前取得的次級報導尚不足以分辨先進封裝設備實際新增量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="262" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">駐菲代表於台灣連結展談台菲半導體合作，菲國 2030 年出口目標 1,100 億美元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣駐菲代表 10 月 24 日在菲律賓馬卡蒂市台灣連結展致詞表示，可結合台菲經濟走廊與呂宋經濟走廊發展半導體合作。他引述菲律賓希望 2030 年半導體與電子產品年出口達 1,100 億美元的目標，另稱截至 2025 年底登記於 PEZA 的台資超過 450 億披索；目前並未公布新的晶圓廠或封測專案核准案。菲律賓現有電子組裝、測試及產業園區基礎，與台灣晶片設計、晶圓製造及設備供應鏈有互補可能。經濟走廊與技術合作在演講中仍屬政策方向，不能作為資本支出或建廠承諾。中央社報導駐菲代表引用截至 2025 年 12 月台企在 PEZA 登記投資超過 450 億披索、創造逾 2 萬個直接就業機會，以及 2026 年前 8 個月雙邊貿易超過 70 億美元。上述歷史統計應與 10 月 24 日的新政策合作表述分開。尚未公布新台菲半導體製造合約、經濟走廊共同施工計畫、合作廠商名單與承諾資本額。地點：菲律賓大馬尼拉地區馬卡蒂市（台灣連結展開幕活動，確切展館未由所取得報導確認）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C43" s="6">
+        <v>46319</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對封裝測試電源、工業控制和設備供應商，可核對兩條經濟走廊是否出現正式的工業園區專案、半導體製程規格與合格客戶。政策目標與既有 PEZA 註冊資料尚不能推估新增設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="246" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">Reuters：越南 Viettel 晶圓廠尚無廠房，DUV 設備採購未定案
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">Reuters 10 月 26 日報導，越南 Viettel 在河內近郊規劃的首座晶圓廠，自 1 月動土以來尚未建起廠房，與 ASML 的 DUV 曝光機洽談亦未成交。知情人士認為 2027 年試產可能延後，但 Viettel 表示計畫仍依階段推進；目前沒有一致確認的新試產日期。越南已有 Intel、Amkor、Hana Micron 等封裝測試基地，Viettel 計畫進入前段晶圓製造，將涉及微影、沉積、蝕刻、製程電源與無塵室設施。封測產能不能替代前段晶圓廠建設。Reuters 實地查訪與衛星影像指出仍無建築，並報導越南當局先前估算建廠約 13 億美元、原定 2027 年試產及 2030 年全面運作。Viettel 回應計畫按階段推進，ASML 未確認設備合約。DUV 型號、正式採購合約、施工許可、製程技轉方及可查證的試產日期均未公布。地點：越南河內近郊 Viettel 規劃晶圓廠基地（確切工業區未披露）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C44" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源、量測與廠務設備業者可追問正式機台採購、技術合約與開工許可。現地觀察和業者回覆存在差異，不能把 2027 年當作已確認的量產日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="198" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">智原取得三星 2 奈米 GAA 雲端晶片設計專案，明年上半年擬認列收入
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">智原 10 月 27 日於法說會表示，與三星晶圓代工、聯電及記憶體供應商合作，取得美國客戶 2 奈米 GAA 雲端 AI 晶片 NRE 專案，金額為數千萬美元。公司預估 2027 年上半年開始認列首筆設計收入，但未公布精確訂單價值、客戶及晶片量產驗證日期。NRE 專案涵蓋先進製程晶片設計及多廠協作；使用三星 2 奈米代工與聯電合作，不等於聯電已可製造 2 奈米晶圓。公司第三季營收 36.64 億元，毛利率 42.5%，歸母淨利 2.79 億元；管理階層說明量產產品比重上升影響毛利率，業外評價利益亦影響淨利成長。未知客戶、製程封裝、NRE 收入精確排程及客戶晶片實際出貨量。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C45" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晶圓製程電源與先進封裝測試業者會確認實際代工場、封裝介面、矽智財驗證及後續晶片試產時程。專案 NRE 金額並非晶圓代工或設備採購支出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="226" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">聯電董事會追加約 32 億美元擴產預算，指向新加坡與南科
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">聯電 10 月 28 日董事會通過約 32 億美元追加擴產預算，公司表示將用於加快新加坡與南科擴建進度，但未提供新產能逐月開出日期。第三季合併營收 742.4 億元、毛利率 34%，12 吋約當晶圓出貨逾 120 萬片，產能利用率達 92%。晶圓代工產能包括成熟節點與 22／28 奈米特殊製程，涉及電源管理 IC、連接晶片、矽光子和工業控制。追加核准資金不等於設備已裝機或支出已發生。聯電原定 2026 年資本支出約 20 億美元，此次為董事會另外核准的擴產預算，不應與季度費用混為一談。公司預估第四季出貨季增 1% 至 3%、稼動率約 91% 至 93%，2027 年平均售價年增 10% 為管理階層預期，非已簽實績。沒有分廠核定支出配置、採購設備清單、投片擴增量、實際動工或轉量產日期；遠期平均售價及 AI 營收占比均為預測。地點：台灣台南科學園區及新加坡既有與規劃廠區（擴產所在區域，未指定新增廠房地址）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C46" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">晶圓製程電源、量測和先進封裝設備供應商需核對新加坡與南科分別核准的工具規格、採購及設備驗收時點。現階段只有董事會授權額與現有稼動率，尚不足以量化未來交付。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="214" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+    <row r="47" ht="214" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1732,22 +1991,22 @@
           </r>
         </is>
       </c>
-      <c r="C40" s="6">
+      <c r="C47" s="6">
         <v>46310</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">伺服器與測試設備物流相關業者須區分轉運申報、原產地文件與出口許可要求。案件仍在調查，不能推論任何已具名供應商涉及違法行為。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="226" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="48" ht="226" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1769,22 +2028,22 @@
           </r>
         </is>
       </c>
-      <c r="C41" s="6">
+      <c r="C48" s="6">
         <v>46324</v>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">晶圓製程電源、測試及廠務設備供應商需區分既有無塵室與重新改裝的機台需求，並確認正式交屋、電力容量與設備資格驗收。交易價格未揭露任何可直接採購的製程設備數量。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="246" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
+    <row r="49" ht="246" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1806,12 +2065,49 @@
           </r>
         </is>
       </c>
-      <c r="C42" s="6">
+      <c r="C49" s="6">
         <v>46324</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">半導體製程電源及量測產業參與者需確認產值統計的產品分項、設備投資和供電成本資料是否分別可得。整體產業產值預測沒有直接揭露單一製造設備的需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="178" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">川湖核准高雄滑軌廠投資預算 197.12 億元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">川湖 10 月 30 日代子公司川益公布，董事會核准 3 廠與 5 廠共 197.12 億元資本支出預算，包含高雄廠房新建及設備購置。另有約 117.33 億元工程價款決議，最終價格依議價簽約確認；105 億元現金增資與可轉債為資金安排，不宜重複算成廠房成本。零組件；伺服器；ODM；工廠；投資。川湖子公司川益董事會通過 3 廠與 5 廠的建置及設備預算，工程款約 117.33 億元仍待議價、簽約。105 億元現金增資及可轉債屬資金籌措，不能與 197.12 億元預算相加。產能擴建尚在預算及工程簽約階段，沒有公布滑軌月產量及驗收日期。地點：台灣高雄市川益科技規劃 3 廠及 5 廠（確切廠址未揭露）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C50" s="6">
+        <v>46325</v>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製造設備與精密量測供應商會核對新廠滑軌產能、機台自動化規格及設備驗收時程。董事會預算核准並未揭露產出或已下達的設備訂單。</t>
         </is>
       </c>
     </row>
